--- a/research/traditional_assets/database/data/ireland/ireland_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_metals_mining.xlsx
@@ -1581,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1718,22 +1718,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09629389045851253</v>
+        <v>0.0962128980954394</v>
       </c>
       <c r="C2">
-        <v>356.5535816279994</v>
+        <v>353.463636761535</v>
       </c>
       <c r="D2">
-        <v>296.2535816279994</v>
+        <v>296.729536761535</v>
       </c>
       <c r="E2">
-        <v>-1.39</v>
+        <v>2.1759</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.5659</v>
       </c>
       <c r="G2">
         <v>60.3</v>
@@ -1754,28 +1754,28 @@
         <v>106.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.17936477</v>
       </c>
       <c r="N2">
-        <v>106.9</v>
+        <v>106.72063523</v>
       </c>
       <c r="O2">
-        <v>13.3625</v>
+        <v>13.34007940375</v>
       </c>
       <c r="P2">
-        <v>93.53750000000001</v>
+        <v>93.38055582625</v>
       </c>
       <c r="Q2">
-        <v>159.3375</v>
+        <v>159.18055582625</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09629389045851253</v>
+        <v>0.09674017484387817</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9929188226047619</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>595.992178397129</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1800,22 +1800,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0962128980954394</v>
+        <v>0.09613190573236624</v>
       </c>
       <c r="C3">
-        <v>353.463636761535</v>
+        <v>350.3752236761715</v>
       </c>
       <c r="D3">
-        <v>296.729536761535</v>
+        <v>297.2070236761714</v>
       </c>
       <c r="E3">
-        <v>2.1759</v>
+        <v>5.7418</v>
       </c>
       <c r="F3">
-        <v>3.5659</v>
+        <v>7.131799999999999</v>
       </c>
       <c r="G3">
         <v>60.3</v>
@@ -1836,28 +1836,28 @@
         <v>106.9</v>
       </c>
       <c r="M3">
-        <v>0.17936477</v>
+        <v>0.35872954</v>
       </c>
       <c r="N3">
-        <v>106.72063523</v>
+        <v>106.54127046</v>
       </c>
       <c r="O3">
-        <v>13.34007940375</v>
+        <v>13.3176588075</v>
       </c>
       <c r="P3">
-        <v>93.38055582625</v>
+        <v>93.22361165250001</v>
       </c>
       <c r="Q3">
-        <v>159.18055582625</v>
+        <v>159.0236116525</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09674017484387817</v>
+        <v>0.09719556707384311</v>
       </c>
       <c r="T3">
-        <v>0.9929188226047619</v>
+        <v>1.00179526478789</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>595.992178397129</v>
+        <v>297.9960891985645</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09613190573236624</v>
+        <v>0.0960509133692931</v>
       </c>
       <c r="C4">
-        <v>350.3752236761715</v>
+        <v>347.2883497784946</v>
       </c>
       <c r="D4">
-        <v>297.2070236761714</v>
+        <v>297.6860497784946</v>
       </c>
       <c r="E4">
-        <v>5.7418</v>
+        <v>9.307699999999999</v>
       </c>
       <c r="F4">
-        <v>7.131799999999999</v>
+        <v>10.6977</v>
       </c>
       <c r="G4">
         <v>60.3</v>
@@ -1918,28 +1918,28 @@
         <v>106.9</v>
       </c>
       <c r="M4">
-        <v>0.35872954</v>
+        <v>0.53809431</v>
       </c>
       <c r="N4">
-        <v>106.54127046</v>
+        <v>106.36190569</v>
       </c>
       <c r="O4">
-        <v>13.3176588075</v>
+        <v>13.29523821125</v>
       </c>
       <c r="P4">
-        <v>93.22361165250001</v>
+        <v>93.06666747875001</v>
       </c>
       <c r="Q4">
-        <v>159.0236116525</v>
+        <v>158.86666747875</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09719556707384311</v>
+        <v>0.09766034883432279</v>
       </c>
       <c r="T4">
-        <v>1.00179526478789</v>
+        <v>1.010854726397475</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>297.9960891985645</v>
+        <v>198.6640594657097</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1964,22 +1964,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0960509133692931</v>
+        <v>0.09596992100621995</v>
       </c>
       <c r="C5">
-        <v>347.2883497784946</v>
+        <v>344.203022522918</v>
       </c>
       <c r="D5">
-        <v>297.6860497784946</v>
+        <v>298.166622522918</v>
       </c>
       <c r="E5">
-        <v>9.307699999999999</v>
+        <v>12.8736</v>
       </c>
       <c r="F5">
-        <v>10.6977</v>
+        <v>14.2636</v>
       </c>
       <c r="G5">
         <v>60.3</v>
@@ -2000,28 +2000,28 @@
         <v>106.9</v>
       </c>
       <c r="M5">
-        <v>0.53809431</v>
+        <v>0.7174590799999999</v>
       </c>
       <c r="N5">
-        <v>106.36190569</v>
+        <v>106.18254092</v>
       </c>
       <c r="O5">
-        <v>13.29523821125</v>
+        <v>13.272817615</v>
       </c>
       <c r="P5">
-        <v>93.06666747875001</v>
+        <v>92.909723305</v>
       </c>
       <c r="Q5">
-        <v>158.86666747875</v>
+        <v>158.709723305</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09766034883432279</v>
+        <v>0.09813481354814579</v>
       </c>
       <c r="T5">
-        <v>1.010854726397475</v>
+        <v>1.020102926790593</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>198.6640594657097</v>
+        <v>148.9980445992823</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2046,22 +2046,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09596992100621995</v>
+        <v>0.09588892864314681</v>
       </c>
       <c r="C6">
-        <v>344.203022522918</v>
+        <v>341.1192494120699</v>
       </c>
       <c r="D6">
-        <v>298.166622522918</v>
+        <v>298.6487494120699</v>
       </c>
       <c r="E6">
-        <v>12.8736</v>
+        <v>16.4395</v>
       </c>
       <c r="F6">
-        <v>14.2636</v>
+        <v>17.8295</v>
       </c>
       <c r="G6">
         <v>60.3</v>
@@ -2082,28 +2082,28 @@
         <v>106.9</v>
       </c>
       <c r="M6">
-        <v>0.7174590799999999</v>
+        <v>0.89682385</v>
       </c>
       <c r="N6">
-        <v>106.18254092</v>
+        <v>106.00317615</v>
       </c>
       <c r="O6">
-        <v>13.272817615</v>
+        <v>13.25039701875</v>
       </c>
       <c r="P6">
-        <v>92.909723305</v>
+        <v>92.75277913125001</v>
       </c>
       <c r="Q6">
-        <v>158.709723305</v>
+        <v>158.55277913125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09813481354814579</v>
+        <v>0.09861926699278613</v>
       </c>
       <c r="T6">
-        <v>1.020102926790593</v>
+        <v>1.029545826139356</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>148.9980445992823</v>
+        <v>119.1984356794258</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2128,22 +2128,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09588892864314681</v>
+        <v>0.09580793628007367</v>
       </c>
       <c r="C7">
-        <v>341.1192494120699</v>
+        <v>338.0370379971827</v>
       </c>
       <c r="D7">
-        <v>298.6487494120699</v>
+        <v>299.1324379971827</v>
       </c>
       <c r="E7">
-        <v>16.4395</v>
+        <v>20.0054</v>
       </c>
       <c r="F7">
-        <v>17.8295</v>
+        <v>21.3954</v>
       </c>
       <c r="G7">
         <v>60.3</v>
@@ -2164,28 +2164,28 @@
         <v>106.9</v>
       </c>
       <c r="M7">
-        <v>0.89682385</v>
+        <v>1.07618862</v>
       </c>
       <c r="N7">
-        <v>106.00317615</v>
+        <v>105.82381138</v>
       </c>
       <c r="O7">
-        <v>13.25039701875</v>
+        <v>13.2279764225</v>
       </c>
       <c r="P7">
-        <v>92.75277913125001</v>
+        <v>92.5958349575</v>
       </c>
       <c r="Q7">
-        <v>158.55277913125</v>
+        <v>158.3958349575</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09861926699278613</v>
+        <v>0.09911402795752519</v>
       </c>
       <c r="T7">
-        <v>1.029545826139356</v>
+        <v>1.039189638240219</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>119.1984356794258</v>
+        <v>99.33202973285483</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2210,22 +2210,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09580793628007367</v>
+        <v>0.09572694391700055</v>
       </c>
       <c r="C8">
-        <v>338.0370379971827</v>
+        <v>334.9563958784881</v>
       </c>
       <c r="D8">
-        <v>299.1324379971827</v>
+        <v>299.6176958784881</v>
       </c>
       <c r="E8">
-        <v>20.0054</v>
+        <v>23.57129999999999</v>
       </c>
       <c r="F8">
-        <v>21.3954</v>
+        <v>24.96129999999999</v>
       </c>
       <c r="G8">
         <v>60.3</v>
@@ -2246,28 +2246,28 @@
         <v>106.9</v>
       </c>
       <c r="M8">
-        <v>1.07618862</v>
+        <v>1.25555339</v>
       </c>
       <c r="N8">
-        <v>105.82381138</v>
+        <v>105.64444661</v>
       </c>
       <c r="O8">
-        <v>13.2279764225</v>
+        <v>13.20555582625</v>
       </c>
       <c r="P8">
-        <v>92.5958349575</v>
+        <v>92.43889078375</v>
       </c>
       <c r="Q8">
-        <v>158.3958349575</v>
+        <v>158.23889078375</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09911402795752519</v>
+        <v>0.09961942894301135</v>
       </c>
       <c r="T8">
-        <v>1.039189638240219</v>
+        <v>1.049040844149704</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>99.33202973285483</v>
+        <v>85.14173977101845</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2292,22 +2292,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09572694391700054</v>
+        <v>0.0956459515539274</v>
       </c>
       <c r="C9">
-        <v>334.9563958784881</v>
+        <v>331.877330705615</v>
       </c>
       <c r="D9">
-        <v>299.6176958784881</v>
+        <v>300.104530705615</v>
       </c>
       <c r="E9">
-        <v>23.5713</v>
+        <v>27.1372</v>
       </c>
       <c r="F9">
-        <v>24.9613</v>
+        <v>28.5272</v>
       </c>
       <c r="G9">
         <v>60.3</v>
@@ -2328,28 +2328,28 @@
         <v>106.9</v>
       </c>
       <c r="M9">
-        <v>1.25555339</v>
+        <v>1.43491816</v>
       </c>
       <c r="N9">
-        <v>105.64444661</v>
+        <v>105.46508184</v>
       </c>
       <c r="O9">
-        <v>13.20555582625</v>
+        <v>13.18313523</v>
       </c>
       <c r="P9">
-        <v>92.43889078375</v>
+        <v>92.28194661000001</v>
       </c>
       <c r="Q9">
-        <v>158.23889078375</v>
+        <v>158.08194661</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09961942894301135</v>
+        <v>0.1001358169064428</v>
       </c>
       <c r="T9">
-        <v>1.049040844149704</v>
+        <v>1.059106206709395</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>85.14173977101842</v>
+        <v>74.49902229964113</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2374,22 +2374,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0956459515539274</v>
+        <v>0.09556495919085425</v>
       </c>
       <c r="C10">
-        <v>331.877330705615</v>
+        <v>328.7998501779909</v>
       </c>
       <c r="D10">
-        <v>300.104530705615</v>
+        <v>300.5929501779909</v>
       </c>
       <c r="E10">
-        <v>27.1372</v>
+        <v>30.7031</v>
       </c>
       <c r="F10">
-        <v>28.5272</v>
+        <v>32.0931</v>
       </c>
       <c r="G10">
         <v>60.3</v>
@@ -2410,28 +2410,28 @@
         <v>106.9</v>
       </c>
       <c r="M10">
-        <v>1.43491816</v>
+        <v>1.61428293</v>
       </c>
       <c r="N10">
-        <v>105.46508184</v>
+        <v>105.28571707</v>
       </c>
       <c r="O10">
-        <v>13.18313523</v>
+        <v>13.16071463375</v>
       </c>
       <c r="P10">
-        <v>92.28194661000001</v>
+        <v>92.12500243625</v>
       </c>
       <c r="Q10">
-        <v>158.08194661</v>
+        <v>157.92500243625</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1001358169064428</v>
+        <v>0.1006635540558838</v>
       </c>
       <c r="T10">
-        <v>1.059106206709395</v>
+        <v>1.069392786028639</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>74.49902229964113</v>
+        <v>66.22135315523656</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2456,22 +2456,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09556495919085425</v>
+        <v>0.09548396682778112</v>
       </c>
       <c r="C11">
-        <v>328.7998501779909</v>
+        <v>325.7239620452484</v>
       </c>
       <c r="D11">
-        <v>300.5929501779909</v>
+        <v>301.0829620452483</v>
       </c>
       <c r="E11">
-        <v>30.7031</v>
+        <v>34.26899999999999</v>
       </c>
       <c r="F11">
-        <v>32.0931</v>
+        <v>35.65899999999999</v>
       </c>
       <c r="G11">
         <v>60.3</v>
@@ -2492,28 +2492,28 @@
         <v>106.9</v>
       </c>
       <c r="M11">
-        <v>1.61428293</v>
+        <v>1.7936477</v>
       </c>
       <c r="N11">
-        <v>105.28571707</v>
+        <v>105.1063523</v>
       </c>
       <c r="O11">
-        <v>13.16071463375</v>
+        <v>13.1382940375</v>
       </c>
       <c r="P11">
-        <v>92.12500243625</v>
+        <v>91.96805826250001</v>
       </c>
       <c r="Q11">
-        <v>157.92500243625</v>
+        <v>157.7680582625</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1006635540558838</v>
+        <v>0.1012030186975346</v>
       </c>
       <c r="T11">
-        <v>1.069392786028639</v>
+        <v>1.079907955999422</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>66.22135315523656</v>
+        <v>59.59921783971291</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2538,22 +2538,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09548396682778112</v>
+        <v>0.09540297446470798</v>
       </c>
       <c r="C12">
-        <v>325.7239620452484</v>
+        <v>322.649674107635</v>
       </c>
       <c r="D12">
-        <v>301.0829620452483</v>
+        <v>301.5745741076349</v>
       </c>
       <c r="E12">
-        <v>34.269</v>
+        <v>37.8349</v>
       </c>
       <c r="F12">
-        <v>35.659</v>
+        <v>39.2249</v>
       </c>
       <c r="G12">
         <v>60.3</v>
@@ -2574,28 +2574,28 @@
         <v>106.9</v>
       </c>
       <c r="M12">
-        <v>1.7936477</v>
+        <v>1.97301247</v>
       </c>
       <c r="N12">
-        <v>105.1063523</v>
+        <v>104.92698753</v>
       </c>
       <c r="O12">
-        <v>13.1382940375</v>
+        <v>13.11587344125</v>
       </c>
       <c r="P12">
-        <v>91.96805826250001</v>
+        <v>91.81111408875</v>
       </c>
       <c r="Q12">
-        <v>157.7680582625</v>
+        <v>157.61111408875</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1012030186975346</v>
+        <v>0.1017546061401213</v>
       </c>
       <c r="T12">
-        <v>1.079907955999422</v>
+        <v>1.090659421924605</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>59.5992178397129</v>
+        <v>54.18110712701173</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2620,22 +2620,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09540297446470798</v>
+        <v>0.09532198210163484</v>
       </c>
       <c r="C13">
-        <v>322.649674107635</v>
+        <v>319.5769942164268</v>
       </c>
       <c r="D13">
-        <v>301.5745741076349</v>
+        <v>302.0677942164268</v>
       </c>
       <c r="E13">
-        <v>37.8349</v>
+        <v>41.4008</v>
       </c>
       <c r="F13">
-        <v>39.2249</v>
+        <v>42.7908</v>
       </c>
       <c r="G13">
         <v>60.3</v>
@@ -2656,28 +2656,28 @@
         <v>106.9</v>
       </c>
       <c r="M13">
-        <v>1.97301247</v>
+        <v>2.15237724</v>
       </c>
       <c r="N13">
-        <v>104.92698753</v>
+        <v>104.74762276</v>
       </c>
       <c r="O13">
-        <v>13.11587344125</v>
+        <v>13.093452845</v>
       </c>
       <c r="P13">
-        <v>91.81111408875</v>
+        <v>91.65416991500001</v>
       </c>
       <c r="Q13">
-        <v>157.61111408875</v>
+        <v>157.454169915</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1017546061401213</v>
+        <v>0.1023187296609487</v>
       </c>
       <c r="T13">
-        <v>1.090659421924605</v>
+        <v>1.101655239348087</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>54.18110712701173</v>
+        <v>49.66601486642742</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2702,22 +2702,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09532198210163484</v>
+        <v>0.09524098973856168</v>
       </c>
       <c r="C14">
-        <v>319.5769942164268</v>
+        <v>316.5059302743466</v>
       </c>
       <c r="D14">
-        <v>302.0677942164268</v>
+        <v>302.5626302743466</v>
       </c>
       <c r="E14">
-        <v>41.4008</v>
+        <v>44.9667</v>
       </c>
       <c r="F14">
-        <v>42.7908</v>
+        <v>46.3567</v>
       </c>
       <c r="G14">
         <v>60.3</v>
@@ -2738,28 +2738,28 @@
         <v>106.9</v>
       </c>
       <c r="M14">
-        <v>2.15237724</v>
+        <v>2.33174201</v>
       </c>
       <c r="N14">
-        <v>104.74762276</v>
+        <v>104.56825799</v>
       </c>
       <c r="O14">
-        <v>13.093452845</v>
+        <v>13.07103224875</v>
       </c>
       <c r="P14">
-        <v>91.65416991500001</v>
+        <v>91.49722574125001</v>
       </c>
       <c r="Q14">
-        <v>157.454169915</v>
+        <v>157.29722574125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1023187296609487</v>
+        <v>0.1028958215385767</v>
       </c>
       <c r="T14">
-        <v>1.101655239348087</v>
+        <v>1.112903834183603</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>49.66601486642742</v>
+        <v>45.84555218439454</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2784,22 +2784,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09524098973856168</v>
+        <v>0.09515999737548855</v>
       </c>
       <c r="C15">
-        <v>316.5059302743466</v>
+        <v>313.4364902359857</v>
       </c>
       <c r="D15">
-        <v>302.5626302743466</v>
+        <v>303.0590902359857</v>
       </c>
       <c r="E15">
-        <v>44.9667</v>
+        <v>48.5326</v>
       </c>
       <c r="F15">
-        <v>46.3567</v>
+        <v>49.9226</v>
       </c>
       <c r="G15">
         <v>60.3</v>
@@ -2820,28 +2820,28 @@
         <v>106.9</v>
       </c>
       <c r="M15">
-        <v>2.33174201</v>
+        <v>2.51110678</v>
       </c>
       <c r="N15">
-        <v>104.56825799</v>
+        <v>104.38889322</v>
       </c>
       <c r="O15">
-        <v>13.07103224875</v>
+        <v>13.0486116525</v>
       </c>
       <c r="P15">
-        <v>91.49722574125001</v>
+        <v>91.3402815675</v>
       </c>
       <c r="Q15">
-        <v>157.29722574125</v>
+        <v>157.1402815675</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1028958215385767</v>
+        <v>0.1034863341575448</v>
       </c>
       <c r="T15">
-        <v>1.112903834183603</v>
+        <v>1.124414024247853</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>45.84555218439454</v>
+        <v>42.57086988550921</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2866,22 +2866,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09515999737548855</v>
+        <v>0.09507900501241542</v>
       </c>
       <c r="C16">
-        <v>313.4364902359857</v>
+        <v>310.3686821082307</v>
       </c>
       <c r="D16">
-        <v>303.0590902359857</v>
+        <v>303.5571821082307</v>
       </c>
       <c r="E16">
-        <v>48.5326</v>
+        <v>52.0985</v>
       </c>
       <c r="F16">
-        <v>49.9226</v>
+        <v>53.4885</v>
       </c>
       <c r="G16">
         <v>60.3</v>
@@ -2902,28 +2902,28 @@
         <v>106.9</v>
       </c>
       <c r="M16">
-        <v>2.51110678</v>
+        <v>2.69047155</v>
       </c>
       <c r="N16">
-        <v>104.38889322</v>
+        <v>104.20952845</v>
       </c>
       <c r="O16">
-        <v>13.0486116525</v>
+        <v>13.02619105625</v>
       </c>
       <c r="P16">
-        <v>91.3402815675</v>
+        <v>91.18333739375001</v>
       </c>
       <c r="Q16">
-        <v>157.1402815675</v>
+        <v>156.98333739375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1034863341575448</v>
+        <v>0.104090741191077</v>
       </c>
       <c r="T16">
-        <v>1.124414024247853</v>
+        <v>1.136195042313614</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>42.57086988550921</v>
+        <v>39.73281189314194</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2948,22 +2948,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0950790050124154</v>
+        <v>0.09499801264934227</v>
       </c>
       <c r="C17">
-        <v>310.3686821082309</v>
+        <v>307.3025139506937</v>
       </c>
       <c r="D17">
-        <v>303.5571821082308</v>
+        <v>304.0569139506937</v>
       </c>
       <c r="E17">
-        <v>52.09849999999999</v>
+        <v>55.66439999999999</v>
       </c>
       <c r="F17">
-        <v>53.48849999999999</v>
+        <v>57.05439999999999</v>
       </c>
       <c r="G17">
         <v>60.3</v>
@@ -2984,28 +2984,28 @@
         <v>106.9</v>
       </c>
       <c r="M17">
-        <v>2.69047155</v>
+        <v>2.86983632</v>
       </c>
       <c r="N17">
-        <v>104.20952845</v>
+        <v>104.03016368</v>
       </c>
       <c r="O17">
-        <v>13.02619105625</v>
+        <v>13.00377046</v>
       </c>
       <c r="P17">
-        <v>91.18333739375001</v>
+        <v>91.02639322</v>
       </c>
       <c r="Q17">
-        <v>156.98333739375</v>
+        <v>156.82639322</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1040907411910769</v>
+        <v>0.1047095388682646</v>
       </c>
       <c r="T17">
-        <v>1.136195042313614</v>
+        <v>1.148256560809512</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>39.73281189314194</v>
+        <v>37.24951114982056</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3030,22 +3030,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09499801264934227</v>
+        <v>0.09491702028626914</v>
       </c>
       <c r="C18">
-        <v>307.3025139506937</v>
+        <v>304.2379938761464</v>
       </c>
       <c r="D18">
-        <v>304.0569139506937</v>
+        <v>304.5582938761464</v>
       </c>
       <c r="E18">
-        <v>55.66439999999999</v>
+        <v>59.2303</v>
       </c>
       <c r="F18">
-        <v>57.05439999999999</v>
+        <v>60.6203</v>
       </c>
       <c r="G18">
         <v>60.3</v>
@@ -3066,28 +3066,28 @@
         <v>106.9</v>
       </c>
       <c r="M18">
-        <v>2.86983632</v>
+        <v>3.04920109</v>
       </c>
       <c r="N18">
-        <v>104.03016368</v>
+        <v>103.85079891</v>
       </c>
       <c r="O18">
-        <v>13.00377046</v>
+        <v>12.98134986375</v>
       </c>
       <c r="P18">
-        <v>91.02639322</v>
+        <v>90.86944904625001</v>
       </c>
       <c r="Q18">
-        <v>156.82639322</v>
+        <v>156.66944904625</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1047095388682646</v>
+        <v>0.1053432473328544</v>
       </c>
       <c r="T18">
-        <v>1.148256560809512</v>
+        <v>1.160608718305311</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>37.24951114982056</v>
+        <v>35.05836343512524</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3112,22 +3112,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09491702028626914</v>
+        <v>0.094836027923196</v>
       </c>
       <c r="C19">
-        <v>304.2379938761464</v>
+        <v>301.1751300509604</v>
       </c>
       <c r="D19">
-        <v>304.5582938761464</v>
+        <v>305.0613300509604</v>
       </c>
       <c r="E19">
-        <v>59.2303</v>
+        <v>62.7962</v>
       </c>
       <c r="F19">
-        <v>60.6203</v>
+        <v>64.1862</v>
       </c>
       <c r="G19">
         <v>60.3</v>
@@ -3148,28 +3148,28 @@
         <v>106.9</v>
       </c>
       <c r="M19">
-        <v>3.04920109</v>
+        <v>3.22856586</v>
       </c>
       <c r="N19">
-        <v>103.85079891</v>
+        <v>103.67143414</v>
       </c>
       <c r="O19">
-        <v>12.98134986375</v>
+        <v>12.9589292675</v>
       </c>
       <c r="P19">
-        <v>90.86944904625001</v>
+        <v>90.71250487250001</v>
       </c>
       <c r="Q19">
-        <v>156.66944904625</v>
+        <v>156.5125048725</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1053432473328544</v>
+        <v>0.1059924121014585</v>
       </c>
       <c r="T19">
-        <v>1.160608718305311</v>
+        <v>1.173262147935155</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>35.05836343512524</v>
+        <v>33.11067657761828</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3194,22 +3194,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09483602792319601</v>
+        <v>0.09475503556012287</v>
       </c>
       <c r="C20">
-        <v>301.1751300509603</v>
+        <v>298.1139306955491</v>
       </c>
       <c r="D20">
-        <v>305.0613300509603</v>
+        <v>305.5660306955491</v>
       </c>
       <c r="E20">
-        <v>62.7962</v>
+        <v>66.3621</v>
       </c>
       <c r="F20">
-        <v>64.1862</v>
+        <v>67.7521</v>
       </c>
       <c r="G20">
         <v>60.3</v>
@@ -3230,28 +3230,28 @@
         <v>106.9</v>
       </c>
       <c r="M20">
-        <v>3.22856586</v>
+        <v>3.40793063</v>
       </c>
       <c r="N20">
-        <v>103.67143414</v>
+        <v>103.49206937</v>
       </c>
       <c r="O20">
-        <v>12.9589292675</v>
+        <v>12.93650867125</v>
       </c>
       <c r="P20">
-        <v>90.71250487250001</v>
+        <v>90.55556069875001</v>
       </c>
       <c r="Q20">
-        <v>156.5125048725</v>
+        <v>156.35556069875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1059924121014585</v>
+        <v>0.1066576056297813</v>
       </c>
       <c r="T20">
-        <v>1.173262147935155</v>
+        <v>1.186228007926228</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>33.11067657761828</v>
+        <v>31.36800938932258</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3276,22 +3276,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09475503556012287</v>
+        <v>0.09467404319704972</v>
       </c>
       <c r="C21">
-        <v>298.1139306955491</v>
+        <v>295.054404084817</v>
       </c>
       <c r="D21">
-        <v>305.5660306955491</v>
+        <v>306.072404084817</v>
       </c>
       <c r="E21">
-        <v>66.3621</v>
+        <v>69.928</v>
       </c>
       <c r="F21">
-        <v>67.7521</v>
+        <v>71.318</v>
       </c>
       <c r="G21">
         <v>60.3</v>
@@ -3312,28 +3312,28 @@
         <v>106.9</v>
       </c>
       <c r="M21">
-        <v>3.40793063</v>
+        <v>3.5872954</v>
       </c>
       <c r="N21">
-        <v>103.49206937</v>
+        <v>103.3127046</v>
       </c>
       <c r="O21">
-        <v>12.93650867125</v>
+        <v>12.914088075</v>
       </c>
       <c r="P21">
-        <v>90.55556069875001</v>
+        <v>90.39861652500001</v>
       </c>
       <c r="Q21">
-        <v>156.35556069875</v>
+        <v>156.198616525</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1066576056297813</v>
+        <v>0.1073394289963121</v>
       </c>
       <c r="T21">
-        <v>1.186228007926228</v>
+        <v>1.199518014417079</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>31.36800938932258</v>
+        <v>29.79960891985645</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3358,22 +3358,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09467404319704972</v>
+        <v>0.09459305083397659</v>
       </c>
       <c r="C22">
-        <v>295.054404084817</v>
+        <v>291.9965585486104</v>
       </c>
       <c r="D22">
-        <v>306.072404084817</v>
+        <v>306.5804585486104</v>
       </c>
       <c r="E22">
-        <v>69.928</v>
+        <v>73.4939</v>
       </c>
       <c r="F22">
-        <v>71.318</v>
+        <v>74.8839</v>
       </c>
       <c r="G22">
         <v>60.3</v>
@@ -3394,28 +3394,28 @@
         <v>106.9</v>
       </c>
       <c r="M22">
-        <v>3.5872954</v>
+        <v>3.76666017</v>
       </c>
       <c r="N22">
-        <v>103.3127046</v>
+        <v>103.13333983</v>
       </c>
       <c r="O22">
-        <v>12.914088075</v>
+        <v>12.89166747875</v>
       </c>
       <c r="P22">
-        <v>90.39861652500001</v>
+        <v>90.24167235125</v>
       </c>
       <c r="Q22">
-        <v>156.198616525</v>
+        <v>156.04167235125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1073394289963121</v>
+        <v>0.1080385137138944</v>
       </c>
       <c r="T22">
-        <v>1.199518014417079</v>
+        <v>1.213144476768458</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>29.79960891985645</v>
+        <v>28.38057992367281</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3440,22 +3440,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09459305083397658</v>
+        <v>0.09451205847090344</v>
       </c>
       <c r="C23">
-        <v>291.9965585486105</v>
+        <v>288.9404024721758</v>
       </c>
       <c r="D23">
-        <v>306.5804585486105</v>
+        <v>307.0902024721757</v>
       </c>
       <c r="E23">
-        <v>73.4939</v>
+        <v>77.0598</v>
       </c>
       <c r="F23">
-        <v>74.8839</v>
+        <v>78.4498</v>
       </c>
       <c r="G23">
         <v>60.3</v>
@@ -3476,28 +3476,28 @@
         <v>106.9</v>
       </c>
       <c r="M23">
-        <v>3.76666017</v>
+        <v>3.94602494</v>
       </c>
       <c r="N23">
-        <v>103.13333983</v>
+        <v>102.95397506</v>
       </c>
       <c r="O23">
-        <v>12.89166747875</v>
+        <v>12.8692468825</v>
       </c>
       <c r="P23">
-        <v>90.24167235125</v>
+        <v>90.08472817750001</v>
       </c>
       <c r="Q23">
-        <v>156.04167235125</v>
+        <v>155.8847281775</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1080385137138944</v>
+        <v>0.1087555236806454</v>
       </c>
       <c r="T23">
-        <v>1.213144476768458</v>
+        <v>1.227120335590385</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>28.38057992367281</v>
+        <v>27.09055356350586</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3522,22 +3522,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09451205847090344</v>
+        <v>0.09443106610783028</v>
       </c>
       <c r="C24">
-        <v>288.9404024721758</v>
+        <v>285.8859442966196</v>
       </c>
       <c r="D24">
-        <v>307.0902024721757</v>
+        <v>307.6016442966196</v>
       </c>
       <c r="E24">
-        <v>77.0598</v>
+        <v>80.62569999999999</v>
       </c>
       <c r="F24">
-        <v>78.4498</v>
+        <v>82.0157</v>
       </c>
       <c r="G24">
         <v>60.3</v>
@@ -3558,28 +3558,28 @@
         <v>106.9</v>
       </c>
       <c r="M24">
-        <v>3.94602494</v>
+        <v>4.125389709999999</v>
       </c>
       <c r="N24">
-        <v>102.95397506</v>
+        <v>102.77461029</v>
       </c>
       <c r="O24">
-        <v>12.8692468825</v>
+        <v>12.84682628625</v>
       </c>
       <c r="P24">
-        <v>90.08472817750001</v>
+        <v>89.92778400375001</v>
       </c>
       <c r="Q24">
-        <v>155.8847281775</v>
+        <v>155.72778400375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1087555236806454</v>
+        <v>0.1094911572828965</v>
       </c>
       <c r="T24">
-        <v>1.227120335590385</v>
+        <v>1.241459203732362</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>27.09055356350586</v>
+        <v>25.91270340857083</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3604,22 +3604,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09443106610783028</v>
+        <v>0.09435007374475717</v>
       </c>
       <c r="C25">
-        <v>285.8859442966196</v>
+        <v>282.8331925193749</v>
       </c>
       <c r="D25">
-        <v>307.6016442966196</v>
+        <v>308.1147925193749</v>
       </c>
       <c r="E25">
-        <v>80.62569999999999</v>
+        <v>84.19159999999999</v>
       </c>
       <c r="F25">
-        <v>82.0157</v>
+        <v>85.58159999999999</v>
       </c>
       <c r="G25">
         <v>60.3</v>
@@ -3640,28 +3640,28 @@
         <v>106.9</v>
       </c>
       <c r="M25">
-        <v>4.125389709999999</v>
+        <v>4.30475448</v>
       </c>
       <c r="N25">
-        <v>102.77461029</v>
+        <v>102.59524552</v>
       </c>
       <c r="O25">
-        <v>12.84682628625</v>
+        <v>12.82440569</v>
       </c>
       <c r="P25">
-        <v>89.92778400375001</v>
+        <v>89.77083983</v>
       </c>
       <c r="Q25">
-        <v>155.72778400375</v>
+        <v>155.57083983</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1094911572828965</v>
+        <v>0.1102461496641542</v>
       </c>
       <c r="T25">
-        <v>1.241459203732362</v>
+        <v>1.256175410509654</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>25.91270340857083</v>
+        <v>24.83300743321371</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3686,22 +3686,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09435007374475715</v>
+        <v>0.09426908138168399</v>
       </c>
       <c r="C26">
-        <v>282.833192519375</v>
+        <v>279.7821556946727</v>
       </c>
       <c r="D26">
-        <v>308.1147925193749</v>
+        <v>308.6296556946727</v>
       </c>
       <c r="E26">
-        <v>84.19159999999999</v>
+        <v>87.75749999999999</v>
       </c>
       <c r="F26">
-        <v>85.58159999999999</v>
+        <v>89.14749999999999</v>
       </c>
       <c r="G26">
         <v>60.3</v>
@@ -3722,28 +3722,28 @@
         <v>106.9</v>
       </c>
       <c r="M26">
-        <v>4.30475448</v>
+        <v>4.484119249999999</v>
       </c>
       <c r="N26">
-        <v>102.59524552</v>
+        <v>102.41588075</v>
       </c>
       <c r="O26">
-        <v>12.82440569</v>
+        <v>12.80198509375</v>
       </c>
       <c r="P26">
-        <v>89.77083983</v>
+        <v>89.61389565625001</v>
       </c>
       <c r="Q26">
-        <v>155.57083983</v>
+        <v>155.41389565625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1102461496641541</v>
+        <v>0.1110212751755787</v>
       </c>
       <c r="T26">
-        <v>1.256175410509654</v>
+        <v>1.271284049467674</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>24.83300743321371</v>
+        <v>23.83968713588516</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3768,22 +3768,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09426908138168399</v>
+        <v>0.09418808901861087</v>
       </c>
       <c r="C27">
-        <v>279.7821556946727</v>
+        <v>276.7328424340156</v>
       </c>
       <c r="D27">
-        <v>308.6296556946727</v>
+        <v>309.1462424340156</v>
       </c>
       <c r="E27">
-        <v>87.75749999999999</v>
+        <v>91.32339999999999</v>
       </c>
       <c r="F27">
-        <v>89.14749999999999</v>
+        <v>92.71339999999999</v>
       </c>
       <c r="G27">
         <v>60.3</v>
@@ -3804,28 +3804,28 @@
         <v>106.9</v>
       </c>
       <c r="M27">
-        <v>4.484119249999999</v>
+        <v>4.663484019999999</v>
       </c>
       <c r="N27">
-        <v>102.41588075</v>
+        <v>102.23651598</v>
       </c>
       <c r="O27">
-        <v>12.80198509375</v>
+        <v>12.7795644975</v>
       </c>
       <c r="P27">
-        <v>89.61389565625001</v>
+        <v>89.4569514825</v>
       </c>
       <c r="Q27">
-        <v>155.41389565625</v>
+        <v>155.2569514825</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1110212751755787</v>
+        <v>0.1118173500251498</v>
       </c>
       <c r="T27">
-        <v>1.271284049467674</v>
+        <v>1.286801030019154</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>23.83968713588516</v>
+        <v>22.92277609219727</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3850,22 +3850,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09418808901861087</v>
+        <v>0.09410709665553774</v>
       </c>
       <c r="C28">
-        <v>276.7328424340156</v>
+        <v>273.6852614066595</v>
       </c>
       <c r="D28">
-        <v>309.1462424340156</v>
+        <v>309.6645614066595</v>
       </c>
       <c r="E28">
-        <v>91.32339999999999</v>
+        <v>94.88930000000001</v>
       </c>
       <c r="F28">
-        <v>92.71339999999999</v>
+        <v>96.27930000000001</v>
       </c>
       <c r="G28">
         <v>60.3</v>
@@ -3886,28 +3886,28 @@
         <v>106.9</v>
       </c>
       <c r="M28">
-        <v>4.663484019999999</v>
+        <v>4.84284879</v>
       </c>
       <c r="N28">
-        <v>102.23651598</v>
+        <v>102.05715121</v>
       </c>
       <c r="O28">
-        <v>12.7795644975</v>
+        <v>12.75714390125</v>
       </c>
       <c r="P28">
-        <v>89.4569514825</v>
+        <v>89.30000730875</v>
       </c>
       <c r="Q28">
-        <v>155.2569514825</v>
+        <v>155.10000730875</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1118173500251498</v>
+        <v>0.1126352351445722</v>
       </c>
       <c r="T28">
-        <v>1.286801030019154</v>
+        <v>1.302743133325469</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>22.92277609219727</v>
+        <v>22.07378438507885</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3932,22 +3932,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09410709665553774</v>
+        <v>0.09402610429246458</v>
       </c>
       <c r="C29">
-        <v>273.6852614066595</v>
+        <v>270.639421340098</v>
       </c>
       <c r="D29">
-        <v>309.6645614066595</v>
+        <v>310.184621340098</v>
       </c>
       <c r="E29">
-        <v>94.88930000000001</v>
+        <v>98.4552</v>
       </c>
       <c r="F29">
-        <v>96.27930000000001</v>
+        <v>99.84520000000001</v>
       </c>
       <c r="G29">
         <v>60.3</v>
@@ -3968,28 +3968,28 @@
         <v>106.9</v>
       </c>
       <c r="M29">
-        <v>4.84284879</v>
+        <v>5.02221356</v>
       </c>
       <c r="N29">
-        <v>102.05715121</v>
+        <v>101.87778644</v>
       </c>
       <c r="O29">
-        <v>12.75714390125</v>
+        <v>12.734723305</v>
       </c>
       <c r="P29">
-        <v>89.30000730875</v>
+        <v>89.14306313500001</v>
       </c>
       <c r="Q29">
-        <v>155.10000730875</v>
+        <v>154.943063135</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1126352351445722</v>
+        <v>0.1134758392950897</v>
       </c>
       <c r="T29">
-        <v>1.302743133325469</v>
+        <v>1.319128072834737</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>22.07378438507885</v>
+        <v>21.28543494275461</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4014,22 +4014,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09402610429246458</v>
+        <v>0.09394511192939145</v>
       </c>
       <c r="C30">
-        <v>270.639421340098</v>
+        <v>267.5953310205516</v>
       </c>
       <c r="D30">
-        <v>310.184621340098</v>
+        <v>310.7064310205516</v>
       </c>
       <c r="E30">
-        <v>98.4552</v>
+        <v>102.0211</v>
       </c>
       <c r="F30">
-        <v>99.84520000000001</v>
+        <v>103.4111</v>
       </c>
       <c r="G30">
         <v>60.3</v>
@@ -4050,28 +4050,28 @@
         <v>106.9</v>
       </c>
       <c r="M30">
-        <v>5.02221356</v>
+        <v>5.20157833</v>
       </c>
       <c r="N30">
-        <v>101.87778644</v>
+        <v>101.69842167</v>
       </c>
       <c r="O30">
-        <v>12.734723305</v>
+        <v>12.71230270875</v>
       </c>
       <c r="P30">
-        <v>89.14306313500001</v>
+        <v>88.98611896125</v>
       </c>
       <c r="Q30">
-        <v>154.943063135</v>
+        <v>154.78611896125</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1134758392950897</v>
+        <v>0.1143401224357626</v>
       </c>
       <c r="T30">
-        <v>1.319128072834737</v>
+        <v>1.335974559935815</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>21.28543494275461</v>
+        <v>20.5514544274872</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4096,22 +4096,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09394511192939142</v>
+        <v>0.09386411956631831</v>
       </c>
       <c r="C31">
-        <v>267.5953310205518</v>
+        <v>264.5529992934637</v>
       </c>
       <c r="D31">
-        <v>310.7064310205518</v>
+        <v>311.2299992934637</v>
       </c>
       <c r="E31">
-        <v>102.0211</v>
+        <v>105.587</v>
       </c>
       <c r="F31">
-        <v>103.4111</v>
+        <v>106.977</v>
       </c>
       <c r="G31">
         <v>60.3</v>
@@ -4132,28 +4132,28 @@
         <v>106.9</v>
       </c>
       <c r="M31">
-        <v>5.201578329999999</v>
+        <v>5.3809431</v>
       </c>
       <c r="N31">
-        <v>101.69842167</v>
+        <v>101.5190569</v>
       </c>
       <c r="O31">
-        <v>12.71230270875</v>
+        <v>12.6898821125</v>
       </c>
       <c r="P31">
-        <v>88.98611896125</v>
+        <v>88.82917478750001</v>
       </c>
       <c r="Q31">
-        <v>154.78611896125</v>
+        <v>154.6291747875</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1143401224357626</v>
+        <v>0.1152290993804547</v>
       </c>
       <c r="T31">
-        <v>1.335974559935815</v>
+        <v>1.353302375239782</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>20.55145442748721</v>
+        <v>19.86640594657097</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4178,22 +4178,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09386411956631831</v>
+        <v>0.09378312720324516</v>
       </c>
       <c r="C32">
-        <v>264.5529992934637</v>
+        <v>261.5124350639995</v>
       </c>
       <c r="D32">
-        <v>311.2299992934637</v>
+        <v>311.7553350639994</v>
       </c>
       <c r="E32">
-        <v>105.587</v>
+        <v>109.1529</v>
       </c>
       <c r="F32">
-        <v>106.977</v>
+        <v>110.5429</v>
       </c>
       <c r="G32">
         <v>60.3</v>
@@ -4214,28 +4214,28 @@
         <v>106.9</v>
       </c>
       <c r="M32">
-        <v>5.3809431</v>
+        <v>5.560307869999999</v>
       </c>
       <c r="N32">
-        <v>101.5190569</v>
+        <v>101.33969213</v>
       </c>
       <c r="O32">
-        <v>12.6898821125</v>
+        <v>12.66746151625</v>
       </c>
       <c r="P32">
-        <v>88.82917478750001</v>
+        <v>88.67223061375</v>
       </c>
       <c r="Q32">
-        <v>154.6291747875</v>
+        <v>154.47223061375</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1152290993804547</v>
+        <v>0.1161438437728191</v>
       </c>
       <c r="T32">
-        <v>1.353302375239782</v>
+        <v>1.371132446059805</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>19.86640594657097</v>
+        <v>19.22555414184287</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4260,22 +4260,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09378312720324516</v>
+        <v>0.09370213484017202</v>
       </c>
       <c r="C33">
-        <v>261.5124350639995</v>
+        <v>258.4736472975511</v>
       </c>
       <c r="D33">
-        <v>311.7553350639994</v>
+        <v>312.282447297551</v>
       </c>
       <c r="E33">
-        <v>109.1529</v>
+        <v>112.7188</v>
       </c>
       <c r="F33">
-        <v>110.5429</v>
+        <v>114.1088</v>
       </c>
       <c r="G33">
         <v>60.3</v>
@@ -4296,28 +4296,28 @@
         <v>106.9</v>
       </c>
       <c r="M33">
-        <v>5.560307869999999</v>
+        <v>5.739672639999999</v>
       </c>
       <c r="N33">
-        <v>101.33969213</v>
+        <v>101.16032736</v>
       </c>
       <c r="O33">
-        <v>12.66746151625</v>
+        <v>12.64504092</v>
       </c>
       <c r="P33">
-        <v>88.67223061375</v>
+        <v>88.51528644000001</v>
       </c>
       <c r="Q33">
-        <v>154.47223061375</v>
+        <v>154.31528644</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1161438437728191</v>
+        <v>0.1170854924120177</v>
       </c>
       <c r="T33">
-        <v>1.371132446059805</v>
+        <v>1.389486930727477</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>19.22555414184287</v>
+        <v>18.62475557491028</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4342,22 +4342,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09370213484017202</v>
+        <v>0.09362114247709888</v>
       </c>
       <c r="C34">
-        <v>258.4736472975511</v>
+        <v>255.4366450202477</v>
       </c>
       <c r="D34">
-        <v>312.282447297551</v>
+        <v>312.8113450202477</v>
       </c>
       <c r="E34">
-        <v>112.7188</v>
+        <v>116.2847</v>
       </c>
       <c r="F34">
-        <v>114.1088</v>
+        <v>117.6747</v>
       </c>
       <c r="G34">
         <v>60.3</v>
@@ -4378,28 +4378,28 @@
         <v>106.9</v>
       </c>
       <c r="M34">
-        <v>5.739672639999999</v>
+        <v>5.91903741</v>
       </c>
       <c r="N34">
-        <v>101.16032736</v>
+        <v>100.98096259</v>
       </c>
       <c r="O34">
-        <v>12.64504092</v>
+        <v>12.62262032375</v>
       </c>
       <c r="P34">
-        <v>88.51528644000001</v>
+        <v>88.35834226625001</v>
       </c>
       <c r="Q34">
-        <v>154.31528644</v>
+        <v>154.15834226625</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1170854924120177</v>
+        <v>0.1180552499658192</v>
       </c>
       <c r="T34">
-        <v>1.389486930727477</v>
+        <v>1.408389310459855</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>18.62475557491028</v>
+        <v>18.06036904233724</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4424,22 +4424,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09362114247709888</v>
+        <v>0.09354015011402575</v>
       </c>
       <c r="C35">
-        <v>255.4366450202477</v>
+        <v>252.401437319471</v>
       </c>
       <c r="D35">
-        <v>312.8113450202477</v>
+        <v>313.342037319471</v>
       </c>
       <c r="E35">
-        <v>116.2847</v>
+        <v>119.8506</v>
       </c>
       <c r="F35">
-        <v>117.6747</v>
+        <v>121.2406</v>
       </c>
       <c r="G35">
         <v>60.3</v>
@@ -4460,28 +4460,28 @@
         <v>106.9</v>
       </c>
       <c r="M35">
-        <v>5.91903741</v>
+        <v>6.09840218</v>
       </c>
       <c r="N35">
-        <v>100.98096259</v>
+        <v>100.80159782</v>
       </c>
       <c r="O35">
-        <v>12.62262032375</v>
+        <v>12.6001997275</v>
       </c>
       <c r="P35">
-        <v>88.35834226625001</v>
+        <v>88.20139809250001</v>
       </c>
       <c r="Q35">
-        <v>154.15834226625</v>
+        <v>154.0013980925</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1180552499658192</v>
+        <v>0.1190543941121602</v>
       </c>
       <c r="T35">
-        <v>1.408389310459855</v>
+        <v>1.427864489578062</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>18.06036904233724</v>
+        <v>17.52918171756262</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4506,22 +4506,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09354015011402575</v>
+        <v>0.09345915775095259</v>
       </c>
       <c r="C36">
-        <v>252.401437319471</v>
+        <v>249.3680333443751</v>
       </c>
       <c r="D36">
-        <v>313.342037319471</v>
+        <v>313.8745333443751</v>
       </c>
       <c r="E36">
-        <v>119.8506</v>
+        <v>123.4165</v>
       </c>
       <c r="F36">
-        <v>121.2406</v>
+        <v>124.8065</v>
       </c>
       <c r="G36">
         <v>60.3</v>
@@ -4542,28 +4542,28 @@
         <v>106.9</v>
       </c>
       <c r="M36">
-        <v>6.09840218</v>
+        <v>6.277766949999999</v>
       </c>
       <c r="N36">
-        <v>100.80159782</v>
+        <v>100.62223305</v>
       </c>
       <c r="O36">
-        <v>12.6001997275</v>
+        <v>12.57777913125</v>
       </c>
       <c r="P36">
-        <v>88.20139809250001</v>
+        <v>88.04445391875001</v>
       </c>
       <c r="Q36">
-        <v>154.0013980925</v>
+        <v>153.84445391875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1190543941121602</v>
+        <v>0.1200842811553117</v>
       </c>
       <c r="T36">
-        <v>1.427864489578062</v>
+        <v>1.44793890497683</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>17.52918171756262</v>
+        <v>17.02834795420369</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4588,22 +4588,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09345915775095259</v>
+        <v>0.09337816538787944</v>
       </c>
       <c r="C37">
-        <v>249.3680333443751</v>
+        <v>246.3364423064126</v>
       </c>
       <c r="D37">
-        <v>313.8745333443751</v>
+        <v>314.4088423064126</v>
       </c>
       <c r="E37">
-        <v>123.4165</v>
+        <v>126.9824</v>
       </c>
       <c r="F37">
-        <v>124.8065</v>
+        <v>128.3724</v>
       </c>
       <c r="G37">
         <v>60.3</v>
@@ -4624,28 +4624,28 @@
         <v>106.9</v>
       </c>
       <c r="M37">
-        <v>6.277766949999999</v>
+        <v>6.45713172</v>
       </c>
       <c r="N37">
-        <v>100.62223305</v>
+        <v>100.44286828</v>
       </c>
       <c r="O37">
-        <v>12.57777913125</v>
+        <v>12.555358535</v>
       </c>
       <c r="P37">
-        <v>88.04445391875001</v>
+        <v>87.887509745</v>
       </c>
       <c r="Q37">
-        <v>153.84445391875</v>
+        <v>153.687509745</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1200842811553117</v>
+        <v>0.1211463521685616</v>
       </c>
       <c r="T37">
-        <v>1.44793890497683</v>
+        <v>1.468640645856809</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>17.02834795420369</v>
+        <v>16.55533828880914</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4670,22 +4670,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09337816538787945</v>
+        <v>0.09329717302480632</v>
       </c>
       <c r="C38">
-        <v>246.3364423064125</v>
+        <v>243.3066734798653</v>
       </c>
       <c r="D38">
-        <v>314.4088423064125</v>
+        <v>314.9449734798653</v>
       </c>
       <c r="E38">
-        <v>126.9824</v>
+        <v>130.5483</v>
       </c>
       <c r="F38">
-        <v>128.3724</v>
+        <v>131.9383</v>
       </c>
       <c r="G38">
         <v>60.3</v>
@@ -4706,28 +4706,28 @@
         <v>106.9</v>
       </c>
       <c r="M38">
-        <v>6.45713172</v>
+        <v>6.63649649</v>
       </c>
       <c r="N38">
-        <v>100.44286828</v>
+        <v>100.26350351</v>
       </c>
       <c r="O38">
-        <v>12.555358535</v>
+        <v>12.53293793875</v>
       </c>
       <c r="P38">
-        <v>87.887509745</v>
+        <v>87.73056557125001</v>
       </c>
       <c r="Q38">
-        <v>153.687509745</v>
+        <v>153.53056557125</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1211463521685616</v>
+        <v>0.1222421397219148</v>
       </c>
       <c r="T38">
-        <v>1.468640645856809</v>
+        <v>1.489999584859962</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>16.55533828880914</v>
+        <v>16.10789671343592</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4752,22 +4752,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09329717302480632</v>
+        <v>0.09321618066173316</v>
       </c>
       <c r="C39">
-        <v>243.3066734798653</v>
+        <v>240.2787362023824</v>
       </c>
       <c r="D39">
-        <v>314.9449734798653</v>
+        <v>315.4829362023824</v>
       </c>
       <c r="E39">
-        <v>130.5483</v>
+        <v>134.1142</v>
       </c>
       <c r="F39">
-        <v>131.9383</v>
+        <v>135.5042</v>
       </c>
       <c r="G39">
         <v>60.3</v>
@@ -4788,28 +4788,28 @@
         <v>106.9</v>
       </c>
       <c r="M39">
-        <v>6.63649649</v>
+        <v>6.815861259999999</v>
       </c>
       <c r="N39">
-        <v>100.26350351</v>
+        <v>100.08413874</v>
       </c>
       <c r="O39">
-        <v>12.53293793875</v>
+        <v>12.5105173425</v>
       </c>
       <c r="P39">
-        <v>87.73056557125001</v>
+        <v>87.57362139750001</v>
       </c>
       <c r="Q39">
-        <v>153.53056557125</v>
+        <v>153.3736213975</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1222421397219148</v>
+        <v>0.1233732752608599</v>
       </c>
       <c r="T39">
-        <v>1.489999584859962</v>
+        <v>1.512047521895475</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>16.10789671343592</v>
+        <v>15.68400469466129</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4834,22 +4834,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09321618066173316</v>
+        <v>0.09313518829866003</v>
       </c>
       <c r="C40">
-        <v>240.2787362023824</v>
+        <v>237.2526398755201</v>
       </c>
       <c r="D40">
-        <v>315.4829362023824</v>
+        <v>316.0227398755201</v>
       </c>
       <c r="E40">
-        <v>134.1142</v>
+        <v>137.6801</v>
       </c>
       <c r="F40">
-        <v>135.5042</v>
+        <v>139.0701</v>
       </c>
       <c r="G40">
         <v>60.3</v>
@@ -4870,28 +4870,28 @@
         <v>106.9</v>
       </c>
       <c r="M40">
-        <v>6.815861259999999</v>
+        <v>6.99522603</v>
       </c>
       <c r="N40">
-        <v>100.08413874</v>
+        <v>99.90477397000001</v>
       </c>
       <c r="O40">
-        <v>12.5105173425</v>
+        <v>12.48809674625</v>
       </c>
       <c r="P40">
-        <v>87.57362139750001</v>
+        <v>87.41667722375001</v>
       </c>
       <c r="Q40">
-        <v>153.3736213975</v>
+        <v>153.21667722375</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1233732752608599</v>
+        <v>0.1245414972109181</v>
       </c>
       <c r="T40">
-        <v>1.512047521895475</v>
+        <v>1.53481834211248</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>15.68400469466129</v>
+        <v>15.28185072813151</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4916,22 +4916,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09313518829866003</v>
+        <v>0.09305419593558689</v>
       </c>
       <c r="C41">
-        <v>237.2526398755201</v>
+        <v>234.2283939652915</v>
       </c>
       <c r="D41">
-        <v>316.0227398755201</v>
+        <v>316.5643939652915</v>
       </c>
       <c r="E41">
-        <v>137.6801</v>
+        <v>141.246</v>
       </c>
       <c r="F41">
-        <v>139.0701</v>
+        <v>142.636</v>
       </c>
       <c r="G41">
         <v>60.3</v>
@@ -4952,28 +4952,28 @@
         <v>106.9</v>
       </c>
       <c r="M41">
-        <v>6.99522603</v>
+        <v>7.1745908</v>
       </c>
       <c r="N41">
-        <v>99.90477397000001</v>
+        <v>99.7254092</v>
       </c>
       <c r="O41">
-        <v>12.48809674625</v>
+        <v>12.46567615</v>
       </c>
       <c r="P41">
-        <v>87.41667722375001</v>
+        <v>87.25973304999999</v>
       </c>
       <c r="Q41">
-        <v>153.21667722375</v>
+        <v>153.05973305</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1245414972109181</v>
+        <v>0.1257486598926448</v>
       </c>
       <c r="T41">
-        <v>1.53481834211248</v>
+        <v>1.558348189670052</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>15.28185072813151</v>
+        <v>14.89980445992822</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4998,22 +4998,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09305419593558689</v>
+        <v>0.09297320357251375</v>
       </c>
       <c r="C42">
-        <v>234.2283939652915</v>
+        <v>231.2060080027185</v>
       </c>
       <c r="D42">
-        <v>316.5643939652915</v>
+        <v>317.1079080027185</v>
       </c>
       <c r="E42">
-        <v>141.246</v>
+        <v>144.8119</v>
       </c>
       <c r="F42">
-        <v>142.636</v>
+        <v>146.2019</v>
       </c>
       <c r="G42">
         <v>60.3</v>
@@ -5034,28 +5034,28 @@
         <v>106.9</v>
       </c>
       <c r="M42">
-        <v>7.1745908</v>
+        <v>7.353955569999999</v>
       </c>
       <c r="N42">
-        <v>99.7254092</v>
+        <v>99.54604443000001</v>
       </c>
       <c r="O42">
-        <v>12.46567615</v>
+        <v>12.44325555375</v>
       </c>
       <c r="P42">
-        <v>87.25973304999999</v>
+        <v>87.10278887625</v>
       </c>
       <c r="Q42">
-        <v>153.05973305</v>
+        <v>152.90278887625</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1257486598926448</v>
+        <v>0.1269967433432437</v>
       </c>
       <c r="T42">
-        <v>1.558348189670052</v>
+        <v>1.582675659178728</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>14.89980445992822</v>
+        <v>14.53639459505193</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5080,22 +5080,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09297320357251375</v>
+        <v>0.09289221120944063</v>
       </c>
       <c r="C43">
-        <v>231.2060080027185</v>
+        <v>228.1854915843917</v>
       </c>
       <c r="D43">
-        <v>317.1079080027185</v>
+        <v>317.6532915843916</v>
       </c>
       <c r="E43">
-        <v>144.8119</v>
+        <v>148.3778</v>
       </c>
       <c r="F43">
-        <v>146.2019</v>
+        <v>149.7678</v>
       </c>
       <c r="G43">
         <v>60.3</v>
@@ -5116,28 +5116,28 @@
         <v>106.9</v>
       </c>
       <c r="M43">
-        <v>7.353955569999999</v>
+        <v>7.53332034</v>
       </c>
       <c r="N43">
-        <v>99.54604443000001</v>
+        <v>99.36667966</v>
       </c>
       <c r="O43">
-        <v>12.44325555375</v>
+        <v>12.4208349575</v>
       </c>
       <c r="P43">
-        <v>87.10278887625</v>
+        <v>86.9458447025</v>
       </c>
       <c r="Q43">
-        <v>152.90278887625</v>
+        <v>152.7458447025</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1269967433432437</v>
+        <v>0.128287864154208</v>
       </c>
       <c r="T43">
-        <v>1.582675659178728</v>
+        <v>1.607842006946324</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>14.53639459505193</v>
+        <v>14.1902899618364</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5162,22 +5162,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09289221120944062</v>
+        <v>0.09281121884636748</v>
       </c>
       <c r="C44">
-        <v>228.1854915843917</v>
+        <v>225.166854373035</v>
       </c>
       <c r="D44">
-        <v>317.6532915843917</v>
+        <v>318.200554373035</v>
       </c>
       <c r="E44">
-        <v>148.3778</v>
+        <v>151.9437</v>
       </c>
       <c r="F44">
-        <v>149.7678</v>
+        <v>153.3337</v>
       </c>
       <c r="G44">
         <v>60.3</v>
@@ -5198,28 +5198,28 @@
         <v>106.9</v>
       </c>
       <c r="M44">
-        <v>7.53332034</v>
+        <v>7.712685109999999</v>
       </c>
       <c r="N44">
-        <v>99.36667966</v>
+        <v>99.18731489000001</v>
       </c>
       <c r="O44">
-        <v>12.4208349575</v>
+        <v>12.39841436125</v>
       </c>
       <c r="P44">
-        <v>86.9458447025</v>
+        <v>86.78890052875001</v>
       </c>
       <c r="Q44">
-        <v>152.7458447025</v>
+        <v>152.58890052875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.128287864154208</v>
+        <v>0.1296242874497675</v>
       </c>
       <c r="T44">
-        <v>1.607842006946324</v>
+        <v>1.633891384460151</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>14.1902899618364</v>
+        <v>13.86028321853789</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5244,22 +5244,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09281121884636748</v>
+        <v>0.09273022648329433</v>
       </c>
       <c r="C45">
-        <v>225.166854373035</v>
+        <v>222.1501060980758</v>
       </c>
       <c r="D45">
-        <v>318.200554373035</v>
+        <v>318.7497060980758</v>
       </c>
       <c r="E45">
-        <v>151.9437</v>
+        <v>155.5096</v>
       </c>
       <c r="F45">
-        <v>153.3337</v>
+        <v>156.8996</v>
       </c>
       <c r="G45">
         <v>60.3</v>
@@ -5280,28 +5280,28 @@
         <v>106.9</v>
       </c>
       <c r="M45">
-        <v>7.712685109999999</v>
+        <v>7.892049879999999</v>
       </c>
       <c r="N45">
-        <v>99.18731489000001</v>
+        <v>99.00795012</v>
       </c>
       <c r="O45">
-        <v>12.39841436125</v>
+        <v>12.375993765</v>
       </c>
       <c r="P45">
-        <v>86.78890052875001</v>
+        <v>86.631956355</v>
       </c>
       <c r="Q45">
-        <v>152.58890052875</v>
+        <v>152.431956355</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1296242874497675</v>
+        <v>0.1310084401487399</v>
       </c>
       <c r="T45">
-        <v>1.633891384460151</v>
+        <v>1.660871096885187</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>13.86028321853789</v>
+        <v>13.54527678175293</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5326,22 +5326,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09273022648329433</v>
+        <v>0.09264923412022122</v>
       </c>
       <c r="C46">
-        <v>222.1501060980758</v>
+        <v>219.1352565562219</v>
       </c>
       <c r="D46">
-        <v>318.7497060980758</v>
+        <v>319.3007565562219</v>
       </c>
       <c r="E46">
-        <v>155.5096</v>
+        <v>159.0755</v>
       </c>
       <c r="F46">
-        <v>156.8996</v>
+        <v>160.4655</v>
       </c>
       <c r="G46">
         <v>60.3</v>
@@ -5362,28 +5362,28 @@
         <v>106.9</v>
       </c>
       <c r="M46">
-        <v>7.892049879999999</v>
+        <v>8.071414649999999</v>
       </c>
       <c r="N46">
-        <v>99.00795012</v>
+        <v>98.82858535000001</v>
       </c>
       <c r="O46">
-        <v>12.375993765</v>
+        <v>12.35357316875</v>
       </c>
       <c r="P46">
-        <v>86.631956355</v>
+        <v>86.47501218125001</v>
       </c>
       <c r="Q46">
-        <v>152.431956355</v>
+        <v>152.27501218125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1310084401487399</v>
+        <v>0.1324429256731295</v>
       </c>
       <c r="T46">
-        <v>1.660871096885187</v>
+        <v>1.688831889762042</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>13.54527678175293</v>
+        <v>13.24427063104731</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5408,22 +5408,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09264923412022122</v>
+        <v>0.09256824175714803</v>
       </c>
       <c r="C47">
-        <v>219.1352565562219</v>
+        <v>216.1223156120452</v>
       </c>
       <c r="D47">
-        <v>319.3007565562219</v>
+        <v>319.8537156120452</v>
       </c>
       <c r="E47">
-        <v>159.0755</v>
+        <v>162.6414</v>
       </c>
       <c r="F47">
-        <v>160.4655</v>
+        <v>164.0314</v>
       </c>
       <c r="G47">
         <v>60.3</v>
@@ -5444,28 +5444,28 @@
         <v>106.9</v>
       </c>
       <c r="M47">
-        <v>8.071414649999999</v>
+        <v>8.250779419999999</v>
       </c>
       <c r="N47">
-        <v>98.82858535000001</v>
+        <v>98.64922058000001</v>
       </c>
       <c r="O47">
-        <v>12.35357316875</v>
+        <v>12.3311525725</v>
       </c>
       <c r="P47">
-        <v>86.47501218125001</v>
+        <v>86.3180680075</v>
       </c>
       <c r="Q47">
-        <v>152.27501218125</v>
+        <v>152.1180680075</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1324429256731295</v>
+        <v>0.1339305402910149</v>
       </c>
       <c r="T47">
-        <v>1.688831889762042</v>
+        <v>1.717828267560262</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>13.24427063104731</v>
+        <v>12.95635170428541</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5490,22 +5490,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09256824175714803</v>
+        <v>0.09310412439407491</v>
       </c>
       <c r="C48">
-        <v>216.1223156120452</v>
+        <v>208.9329672394439</v>
       </c>
       <c r="D48">
-        <v>319.8537156120452</v>
+        <v>316.2302672394438</v>
       </c>
       <c r="E48">
-        <v>162.6414</v>
+        <v>166.2073</v>
       </c>
       <c r="F48">
-        <v>164.0314</v>
+        <v>167.5973</v>
       </c>
       <c r="G48">
         <v>60.3</v>
@@ -5526,45 +5526,45 @@
         <v>106.9</v>
       </c>
       <c r="M48">
-        <v>8.250779419999999</v>
+        <v>8.681540139999999</v>
       </c>
       <c r="N48">
-        <v>98.64922058000001</v>
+        <v>98.21845986000001</v>
       </c>
       <c r="O48">
-        <v>12.3311525725</v>
+        <v>12.2773074825</v>
       </c>
       <c r="P48">
-        <v>86.3180680075</v>
+        <v>85.9411523775</v>
       </c>
       <c r="Q48">
-        <v>152.1180680075</v>
+        <v>151.7411523775</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1339305402910149</v>
+        <v>0.1354742913095753</v>
       </c>
       <c r="T48">
-        <v>1.717828267560262</v>
+        <v>1.747918848294264</v>
       </c>
       <c r="U48">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y48">
-        <v>12.95635170428541</v>
+        <v>12.31348335388794</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5572,22 +5572,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09310412439407491</v>
+        <v>0.09303625703100177</v>
       </c>
       <c r="C49">
-        <v>208.9329672394439</v>
+        <v>205.8214155665641</v>
       </c>
       <c r="D49">
-        <v>316.2302672394438</v>
+        <v>316.684615566564</v>
       </c>
       <c r="E49">
-        <v>166.2073</v>
+        <v>169.7732</v>
       </c>
       <c r="F49">
-        <v>167.5973</v>
+        <v>171.1632</v>
       </c>
       <c r="G49">
         <v>60.3</v>
@@ -5608,28 +5608,28 @@
         <v>106.9</v>
       </c>
       <c r="M49">
-        <v>8.681540139999999</v>
+        <v>8.866253759999999</v>
       </c>
       <c r="N49">
-        <v>98.21845986000001</v>
+        <v>98.03374624</v>
       </c>
       <c r="O49">
-        <v>12.2773074825</v>
+        <v>12.25421828</v>
       </c>
       <c r="P49">
-        <v>85.9411523775</v>
+        <v>85.77952796</v>
       </c>
       <c r="Q49">
-        <v>151.7411523775</v>
+        <v>151.57952796</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1354742913095753</v>
+        <v>0.1370774173673111</v>
       </c>
       <c r="T49">
-        <v>1.747918848294264</v>
+        <v>1.779166759056496</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>12.31348335388794</v>
+        <v>12.05695245068194</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5654,22 +5654,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09303625703100175</v>
+        <v>0.09296838966792863</v>
       </c>
       <c r="C50">
-        <v>205.8214155665641</v>
+        <v>202.7111713550199</v>
       </c>
       <c r="D50">
-        <v>316.6846155665641</v>
+        <v>317.1402713550199</v>
       </c>
       <c r="E50">
-        <v>169.7732</v>
+        <v>173.3391</v>
       </c>
       <c r="F50">
-        <v>171.1632</v>
+        <v>174.7291</v>
       </c>
       <c r="G50">
         <v>60.3</v>
@@ -5690,28 +5690,28 @@
         <v>106.9</v>
       </c>
       <c r="M50">
-        <v>8.866253759999999</v>
+        <v>9.050967379999999</v>
       </c>
       <c r="N50">
-        <v>98.03374624</v>
+        <v>97.84903262</v>
       </c>
       <c r="O50">
-        <v>12.25421828</v>
+        <v>12.2311290775</v>
       </c>
       <c r="P50">
-        <v>85.77952796</v>
+        <v>85.6179035425</v>
       </c>
       <c r="Q50">
-        <v>151.57952796</v>
+        <v>151.4179035425</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1370774173673111</v>
+        <v>0.1387434111135855</v>
       </c>
       <c r="T50">
-        <v>1.779166759056496</v>
+        <v>1.811640078083915</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>12.05695245068194</v>
+        <v>11.81089219658639</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5736,22 +5736,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09296838966792863</v>
+        <v>0.0929005223048555</v>
       </c>
       <c r="C51">
-        <v>202.7111713550199</v>
+        <v>199.6022402565929</v>
       </c>
       <c r="D51">
-        <v>317.1402713550199</v>
+        <v>317.5972402565928</v>
       </c>
       <c r="E51">
-        <v>173.3391</v>
+        <v>176.905</v>
       </c>
       <c r="F51">
-        <v>174.7291</v>
+        <v>178.295</v>
       </c>
       <c r="G51">
         <v>60.3</v>
@@ -5772,28 +5772,28 @@
         <v>106.9</v>
       </c>
       <c r="M51">
-        <v>9.050967379999999</v>
+        <v>9.235681</v>
       </c>
       <c r="N51">
-        <v>97.84903262</v>
+        <v>97.66431900000001</v>
       </c>
       <c r="O51">
-        <v>12.2311290775</v>
+        <v>12.208039875</v>
       </c>
       <c r="P51">
-        <v>85.6179035425</v>
+        <v>85.45627912500001</v>
       </c>
       <c r="Q51">
-        <v>151.4179035425</v>
+        <v>151.256279125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1387434111135855</v>
+        <v>0.140476044609711</v>
       </c>
       <c r="T51">
-        <v>1.811640078083915</v>
+        <v>1.84541232987243</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>11.81089219658639</v>
+        <v>11.57467435265467</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5818,22 +5818,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0929005223048555</v>
+        <v>0.09283265494178236</v>
       </c>
       <c r="C52">
-        <v>199.6022402565929</v>
+        <v>196.4946279556862</v>
       </c>
       <c r="D52">
-        <v>317.5972402565928</v>
+        <v>318.0555279556862</v>
       </c>
       <c r="E52">
-        <v>176.905</v>
+        <v>180.4709</v>
       </c>
       <c r="F52">
-        <v>178.295</v>
+        <v>181.8609</v>
       </c>
       <c r="G52">
         <v>60.3</v>
@@ -5854,28 +5854,28 @@
         <v>106.9</v>
       </c>
       <c r="M52">
-        <v>9.235681</v>
+        <v>9.42039462</v>
       </c>
       <c r="N52">
-        <v>97.66431900000001</v>
+        <v>97.47960538000001</v>
       </c>
       <c r="O52">
-        <v>12.208039875</v>
+        <v>12.1849506725</v>
       </c>
       <c r="P52">
-        <v>85.45627912500001</v>
+        <v>85.2946547075</v>
       </c>
       <c r="Q52">
-        <v>151.256279125</v>
+        <v>151.0946547075</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.140476044609711</v>
+        <v>0.1422793978403722</v>
       </c>
       <c r="T52">
-        <v>1.84541232987243</v>
+        <v>1.880563040917619</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>11.57467435265467</v>
+        <v>11.34771995358301</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5900,22 +5900,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09283265494178236</v>
+        <v>0.09276478757870921</v>
       </c>
       <c r="C53">
-        <v>196.4946279556862</v>
+        <v>193.3883401695606</v>
       </c>
       <c r="D53">
-        <v>318.0555279556862</v>
+        <v>318.5151401695606</v>
       </c>
       <c r="E53">
-        <v>180.4709</v>
+        <v>184.0368</v>
       </c>
       <c r="F53">
-        <v>181.8609</v>
+        <v>185.4268</v>
       </c>
       <c r="G53">
         <v>60.3</v>
@@ -5936,28 +5936,28 @@
         <v>106.9</v>
       </c>
       <c r="M53">
-        <v>9.42039462</v>
+        <v>9.60510824</v>
       </c>
       <c r="N53">
-        <v>97.47960538000001</v>
+        <v>97.29489176000001</v>
       </c>
       <c r="O53">
-        <v>12.1849506725</v>
+        <v>12.16186147</v>
       </c>
       <c r="P53">
-        <v>85.2946547075</v>
+        <v>85.13303029000001</v>
       </c>
       <c r="Q53">
-        <v>151.0946547075</v>
+        <v>150.93303029</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1422793978403722</v>
+        <v>0.1441578907889775</v>
       </c>
       <c r="T53">
-        <v>1.880563040917619</v>
+        <v>1.917178364923024</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>11.34771995358301</v>
+        <v>11.12949456986026</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5982,22 +5982,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09276478757870921</v>
+        <v>0.09269692021563607</v>
       </c>
       <c r="C54">
-        <v>193.3883401695606</v>
+        <v>190.2833826485717</v>
       </c>
       <c r="D54">
-        <v>318.5151401695606</v>
+        <v>318.9760826485717</v>
       </c>
       <c r="E54">
-        <v>184.0368</v>
+        <v>187.6027</v>
       </c>
       <c r="F54">
-        <v>185.4268</v>
+        <v>188.9927</v>
       </c>
       <c r="G54">
         <v>60.3</v>
@@ -6018,28 +6018,28 @@
         <v>106.9</v>
       </c>
       <c r="M54">
-        <v>9.60510824</v>
+        <v>9.789821859999998</v>
       </c>
       <c r="N54">
-        <v>97.29489176000001</v>
+        <v>97.11017814</v>
       </c>
       <c r="O54">
-        <v>12.16186147</v>
+        <v>12.1387722675</v>
       </c>
       <c r="P54">
-        <v>85.13303029000001</v>
+        <v>84.9714058725</v>
       </c>
       <c r="Q54">
-        <v>150.93303029</v>
+        <v>150.7714058725</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1441578907889775</v>
+        <v>0.1461163196077363</v>
       </c>
       <c r="T54">
-        <v>1.917178364923024</v>
+        <v>1.955351787822277</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.12949456986026</v>
+        <v>10.91950410627799</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6064,22 +6064,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09269692021563607</v>
+        <v>0.09262905285256293</v>
       </c>
       <c r="C55">
-        <v>190.2833826485717</v>
+        <v>187.1797611764103</v>
       </c>
       <c r="D55">
-        <v>318.9760826485717</v>
+        <v>319.4383611764103</v>
       </c>
       <c r="E55">
-        <v>187.6027</v>
+        <v>191.1686</v>
       </c>
       <c r="F55">
-        <v>188.9927</v>
+        <v>192.5586</v>
       </c>
       <c r="G55">
         <v>60.3</v>
@@ -6100,28 +6100,28 @@
         <v>106.9</v>
       </c>
       <c r="M55">
-        <v>9.789821859999998</v>
+        <v>9.97453548</v>
       </c>
       <c r="N55">
-        <v>97.11017814</v>
+        <v>96.92546452000001</v>
       </c>
       <c r="O55">
-        <v>12.1387722675</v>
+        <v>12.115683065</v>
       </c>
       <c r="P55">
-        <v>84.9714058725</v>
+        <v>84.80978145500001</v>
       </c>
       <c r="Q55">
-        <v>150.7714058725</v>
+        <v>150.609781455</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1461163196077363</v>
+        <v>0.1481598975055716</v>
       </c>
       <c r="T55">
-        <v>1.955351787822277</v>
+        <v>1.995184924760627</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.91950410627799</v>
+        <v>10.71729106727284</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6146,22 +6146,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09262905285256293</v>
+        <v>0.09256118548948979</v>
       </c>
       <c r="C56">
-        <v>187.1797611764103</v>
+        <v>184.077481570344</v>
       </c>
       <c r="D56">
-        <v>319.4383611764103</v>
+        <v>319.901981570344</v>
       </c>
       <c r="E56">
-        <v>191.1686</v>
+        <v>194.7345</v>
       </c>
       <c r="F56">
-        <v>192.5586</v>
+        <v>196.1245</v>
       </c>
       <c r="G56">
         <v>60.3</v>
@@ -6182,28 +6182,28 @@
         <v>106.9</v>
       </c>
       <c r="M56">
-        <v>9.97453548</v>
+        <v>10.1592491</v>
       </c>
       <c r="N56">
-        <v>96.92546452000001</v>
+        <v>96.74075090000001</v>
       </c>
       <c r="O56">
-        <v>12.115683065</v>
+        <v>12.0925938625</v>
       </c>
       <c r="P56">
-        <v>84.80978145500001</v>
+        <v>84.64815703750001</v>
       </c>
       <c r="Q56">
-        <v>150.609781455</v>
+        <v>150.4481570375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1481598975055716</v>
+        <v>0.1502943010877551</v>
       </c>
       <c r="T56">
-        <v>1.995184924760627</v>
+        <v>2.036788423340682</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>10.71729106727284</v>
+        <v>10.52243122968606</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6228,22 +6228,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09256118548948979</v>
+        <v>0.09249331812641665</v>
       </c>
       <c r="C57">
-        <v>184.077481570344</v>
+        <v>180.9765496814616</v>
       </c>
       <c r="D57">
-        <v>319.901981570344</v>
+        <v>320.3669496814616</v>
       </c>
       <c r="E57">
-        <v>194.7345</v>
+        <v>198.3004</v>
       </c>
       <c r="F57">
-        <v>196.1245</v>
+        <v>199.6904</v>
       </c>
       <c r="G57">
         <v>60.3</v>
@@ -6264,28 +6264,28 @@
         <v>106.9</v>
       </c>
       <c r="M57">
-        <v>10.1592491</v>
+        <v>10.34396272</v>
       </c>
       <c r="N57">
-        <v>96.74075090000001</v>
+        <v>96.55603728</v>
       </c>
       <c r="O57">
-        <v>12.0925938625</v>
+        <v>12.06950466</v>
       </c>
       <c r="P57">
-        <v>84.64815703750001</v>
+        <v>84.48653261999999</v>
       </c>
       <c r="Q57">
-        <v>150.4481570375</v>
+        <v>150.28653262</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1502943010877551</v>
+        <v>0.1525257230145833</v>
       </c>
       <c r="T57">
-        <v>2.036788423340682</v>
+        <v>2.080282990038012</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>10.52243122968606</v>
+        <v>10.33453067201309</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6310,22 +6310,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09249331812641665</v>
+        <v>0.09242545076334351</v>
       </c>
       <c r="C58">
-        <v>180.9765496814616</v>
+        <v>177.8769713949187</v>
       </c>
       <c r="D58">
-        <v>320.3669496814616</v>
+        <v>320.8332713949187</v>
       </c>
       <c r="E58">
-        <v>198.3004</v>
+        <v>201.8663</v>
       </c>
       <c r="F58">
-        <v>199.6904</v>
+        <v>203.2563</v>
       </c>
       <c r="G58">
         <v>60.3</v>
@@ -6346,28 +6346,28 @@
         <v>106.9</v>
       </c>
       <c r="M58">
-        <v>10.34396272</v>
+        <v>10.52867634</v>
       </c>
       <c r="N58">
-        <v>96.55603728</v>
+        <v>96.37132366</v>
       </c>
       <c r="O58">
-        <v>12.06950466</v>
+        <v>12.0464154575</v>
       </c>
       <c r="P58">
-        <v>84.48653261999999</v>
+        <v>84.3249082025</v>
       </c>
       <c r="Q58">
-        <v>150.28653262</v>
+        <v>150.1249082025</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1525257230145833</v>
+        <v>0.1548609320077756</v>
       </c>
       <c r="T58">
-        <v>2.080282990038012</v>
+        <v>2.125800559837543</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>10.33453067201309</v>
+        <v>10.15322311636374</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6392,22 +6392,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09242545076334351</v>
+        <v>0.09235758340027037</v>
       </c>
       <c r="C59">
-        <v>177.8769713949187</v>
+        <v>174.778752630186</v>
       </c>
       <c r="D59">
-        <v>320.8332713949187</v>
+        <v>321.300952630186</v>
       </c>
       <c r="E59">
-        <v>201.8663</v>
+        <v>205.4322</v>
       </c>
       <c r="F59">
-        <v>203.2563</v>
+        <v>206.8222</v>
       </c>
       <c r="G59">
         <v>60.3</v>
@@ -6428,28 +6428,28 @@
         <v>106.9</v>
       </c>
       <c r="M59">
-        <v>10.52867634</v>
+        <v>10.71338996</v>
       </c>
       <c r="N59">
-        <v>96.37132366</v>
+        <v>96.18661004000001</v>
       </c>
       <c r="O59">
-        <v>12.0464154575</v>
+        <v>12.023326255</v>
       </c>
       <c r="P59">
-        <v>84.3249082025</v>
+        <v>84.163283785</v>
       </c>
       <c r="Q59">
-        <v>150.1249082025</v>
+        <v>149.963283785</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1548609320077756</v>
+        <v>0.1573073414292152</v>
       </c>
       <c r="T59">
-        <v>2.125800559837543</v>
+        <v>2.173485632960862</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.15322311636374</v>
+        <v>9.978167545391953</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6474,22 +6474,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09235758340027037</v>
+        <v>0.09316734103719723</v>
       </c>
       <c r="C60">
-        <v>174.778752630186</v>
+        <v>165.7201250578307</v>
       </c>
       <c r="D60">
-        <v>321.300952630186</v>
+        <v>315.8082250578307</v>
       </c>
       <c r="E60">
-        <v>205.4322</v>
+        <v>208.9981</v>
       </c>
       <c r="F60">
-        <v>206.8222</v>
+        <v>210.3881</v>
       </c>
       <c r="G60">
         <v>60.3</v>
@@ -6510,45 +6510,45 @@
         <v>106.9</v>
       </c>
       <c r="M60">
-        <v>10.71338996</v>
+        <v>11.25576335</v>
       </c>
       <c r="N60">
-        <v>96.18661004000001</v>
+        <v>95.64423665000001</v>
       </c>
       <c r="O60">
-        <v>12.023326255</v>
+        <v>11.95552958125</v>
       </c>
       <c r="P60">
-        <v>84.163283785</v>
+        <v>83.68870706875001</v>
       </c>
       <c r="Q60">
-        <v>149.963283785</v>
+        <v>149.48870706875</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1573073414292152</v>
+        <v>0.159873087895603</v>
       </c>
       <c r="T60">
-        <v>2.173485632960861</v>
+        <v>2.223496807212147</v>
       </c>
       <c r="U60">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V60">
         <v>0.125</v>
       </c>
       <c r="W60">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>9.978167545391955</v>
+        <v>9.497356747465735</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6556,22 +6556,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09316734103719723</v>
+        <v>0.09311434867412409</v>
       </c>
       <c r="C61">
-        <v>165.7201250578307</v>
+        <v>162.5079322226279</v>
       </c>
       <c r="D61">
-        <v>315.8082250578307</v>
+        <v>316.1619322226279</v>
       </c>
       <c r="E61">
-        <v>208.9981</v>
+        <v>212.564</v>
       </c>
       <c r="F61">
-        <v>210.3881</v>
+        <v>213.954</v>
       </c>
       <c r="G61">
         <v>60.3</v>
@@ -6592,28 +6592,28 @@
         <v>106.9</v>
       </c>
       <c r="M61">
-        <v>11.25576335</v>
+        <v>11.446539</v>
       </c>
       <c r="N61">
-        <v>95.64423665000001</v>
+        <v>95.453461</v>
       </c>
       <c r="O61">
-        <v>11.95552958125</v>
+        <v>11.931682625</v>
       </c>
       <c r="P61">
-        <v>83.68870706875001</v>
+        <v>83.521778375</v>
       </c>
       <c r="Q61">
-        <v>149.48870706875</v>
+        <v>149.321778375</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.159873087895603</v>
+        <v>0.1625671216853102</v>
       </c>
       <c r="T61">
-        <v>2.223496807212147</v>
+        <v>2.276008540175997</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>9.497356747465735</v>
+        <v>9.339067468341305</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6638,22 +6638,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09311434867412409</v>
+        <v>0.09306135631105095</v>
       </c>
       <c r="C62">
-        <v>162.5079322226279</v>
+        <v>159.2965325842337</v>
       </c>
       <c r="D62">
-        <v>316.1619322226279</v>
+        <v>316.5164325842337</v>
       </c>
       <c r="E62">
-        <v>212.564</v>
+        <v>216.1299</v>
       </c>
       <c r="F62">
-        <v>213.954</v>
+        <v>217.5199</v>
       </c>
       <c r="G62">
         <v>60.3</v>
@@ -6674,28 +6674,28 @@
         <v>106.9</v>
       </c>
       <c r="M62">
-        <v>11.446539</v>
+        <v>11.63731465</v>
       </c>
       <c r="N62">
-        <v>95.453461</v>
+        <v>95.26268535000001</v>
       </c>
       <c r="O62">
-        <v>11.931682625</v>
+        <v>11.90783566875</v>
       </c>
       <c r="P62">
-        <v>83.521778375</v>
+        <v>83.35484968125002</v>
       </c>
       <c r="Q62">
-        <v>149.321778375</v>
+        <v>149.15484968125</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1625671216853102</v>
+        <v>0.1653993110539768</v>
       </c>
       <c r="T62">
-        <v>2.276008540175997</v>
+        <v>2.331213182522608</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>9.339067468341305</v>
+        <v>9.185968001647186</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6720,22 +6720,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09306135631105095</v>
+        <v>0.0930083639479778</v>
       </c>
       <c r="C63">
-        <v>159.2965325842337</v>
+        <v>156.0859288137874</v>
       </c>
       <c r="D63">
-        <v>316.5164325842337</v>
+        <v>316.8717288137874</v>
       </c>
       <c r="E63">
-        <v>216.1299</v>
+        <v>219.6958</v>
       </c>
       <c r="F63">
-        <v>217.5199</v>
+        <v>221.0858</v>
       </c>
       <c r="G63">
         <v>60.3</v>
@@ -6756,28 +6756,28 @@
         <v>106.9</v>
       </c>
       <c r="M63">
-        <v>11.63731465</v>
+        <v>11.8280903</v>
       </c>
       <c r="N63">
-        <v>95.26268535000001</v>
+        <v>95.07190970000001</v>
       </c>
       <c r="O63">
-        <v>11.90783566875</v>
+        <v>11.8839887125</v>
       </c>
       <c r="P63">
-        <v>83.35484968125002</v>
+        <v>83.18792098750001</v>
       </c>
       <c r="Q63">
-        <v>149.15484968125</v>
+        <v>148.9879209875</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1653993110539768</v>
+        <v>0.1683805630209942</v>
       </c>
       <c r="T63">
-        <v>2.331213182522608</v>
+        <v>2.389323332361146</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>9.185968001647186</v>
+        <v>9.03780722742707</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6802,22 +6802,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0930083639479778</v>
+        <v>0.09295537158490468</v>
       </c>
       <c r="C64">
-        <v>156.0859288137874</v>
+        <v>152.8761235944356</v>
       </c>
       <c r="D64">
-        <v>316.8717288137874</v>
+        <v>317.2278235944356</v>
       </c>
       <c r="E64">
-        <v>219.6958</v>
+        <v>223.2617</v>
       </c>
       <c r="F64">
-        <v>221.0858</v>
+        <v>224.6517</v>
       </c>
       <c r="G64">
         <v>60.3</v>
@@ -6838,28 +6838,28 @@
         <v>106.9</v>
       </c>
       <c r="M64">
-        <v>11.8280903</v>
+        <v>12.01886595</v>
       </c>
       <c r="N64">
-        <v>95.07190970000001</v>
+        <v>94.88113405000001</v>
       </c>
       <c r="O64">
-        <v>11.8839887125</v>
+        <v>11.86014175625</v>
       </c>
       <c r="P64">
-        <v>83.18792098750001</v>
+        <v>83.02099229375001</v>
       </c>
       <c r="Q64">
-        <v>148.9879209875</v>
+        <v>148.82099229375</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1683805630209942</v>
+        <v>0.1715229637429856</v>
       </c>
       <c r="T64">
-        <v>2.389323332361146</v>
+        <v>2.450574571380145</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>9.03780722742707</v>
+        <v>8.894349969848863</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6884,22 +6884,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09295537158490468</v>
+        <v>0.09290237922183152</v>
       </c>
       <c r="C65">
-        <v>152.8761235944356</v>
+        <v>149.6671196213996</v>
       </c>
       <c r="D65">
-        <v>317.2278235944356</v>
+        <v>317.5847196213996</v>
       </c>
       <c r="E65">
-        <v>223.2617</v>
+        <v>226.8276</v>
       </c>
       <c r="F65">
-        <v>224.6517</v>
+        <v>228.2176</v>
       </c>
       <c r="G65">
         <v>60.3</v>
@@ -6920,28 +6920,28 @@
         <v>106.9</v>
       </c>
       <c r="M65">
-        <v>12.01886595</v>
+        <v>12.2096416</v>
       </c>
       <c r="N65">
-        <v>94.88113405000001</v>
+        <v>94.69035840000001</v>
       </c>
       <c r="O65">
-        <v>11.86014175625</v>
+        <v>11.8362948</v>
       </c>
       <c r="P65">
-        <v>83.02099229375001</v>
+        <v>82.8540636</v>
       </c>
       <c r="Q65">
-        <v>148.82099229375</v>
+        <v>148.6540636</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1715229637429856</v>
+        <v>0.1748399422828653</v>
       </c>
       <c r="T65">
-        <v>2.450574571380145</v>
+        <v>2.515228657011312</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.894349969848863</v>
+        <v>8.755375751569975</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6966,22 +6966,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09290237922183152</v>
+        <v>0.09284938685875838</v>
       </c>
       <c r="C66">
-        <v>149.6671196213996</v>
+        <v>146.458919602043</v>
       </c>
       <c r="D66">
-        <v>317.5847196213996</v>
+        <v>317.9424196020429</v>
       </c>
       <c r="E66">
-        <v>226.8276</v>
+        <v>230.3935</v>
       </c>
       <c r="F66">
-        <v>228.2176</v>
+        <v>231.7835</v>
       </c>
       <c r="G66">
         <v>60.3</v>
@@ -7002,28 +7002,28 @@
         <v>106.9</v>
       </c>
       <c r="M66">
-        <v>12.2096416</v>
+        <v>12.40041725</v>
       </c>
       <c r="N66">
-        <v>94.69035840000001</v>
+        <v>94.49958275</v>
       </c>
       <c r="O66">
-        <v>11.8362948</v>
+        <v>11.81244784375</v>
       </c>
       <c r="P66">
-        <v>82.8540636</v>
+        <v>82.68713490625001</v>
       </c>
       <c r="Q66">
-        <v>148.6540636</v>
+        <v>148.48713490625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1748399422828653</v>
+        <v>0.1783464624535954</v>
       </c>
       <c r="T66">
-        <v>2.515228657011312</v>
+        <v>2.583577261821402</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.755375751569975</v>
+        <v>8.62067766308428</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7048,22 +7048,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09284938685875838</v>
+        <v>0.09279639449568525</v>
       </c>
       <c r="C67">
-        <v>146.458919602043</v>
+        <v>143.2515262559406</v>
       </c>
       <c r="D67">
-        <v>317.9424196020429</v>
+        <v>318.3009262559406</v>
       </c>
       <c r="E67">
-        <v>230.3935</v>
+        <v>233.9594</v>
       </c>
       <c r="F67">
-        <v>231.7835</v>
+        <v>235.3494</v>
       </c>
       <c r="G67">
         <v>60.3</v>
@@ -7084,28 +7084,28 @@
         <v>106.9</v>
       </c>
       <c r="M67">
-        <v>12.40041725</v>
+        <v>12.5911929</v>
       </c>
       <c r="N67">
-        <v>94.49958275</v>
+        <v>94.30880710000001</v>
       </c>
       <c r="O67">
-        <v>11.81244784375</v>
+        <v>11.7886008875</v>
       </c>
       <c r="P67">
-        <v>82.68713490625001</v>
+        <v>82.52020621250001</v>
       </c>
       <c r="Q67">
-        <v>148.48713490625</v>
+        <v>148.3202062125</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1783464624535954</v>
+        <v>0.1820592485167213</v>
       </c>
       <c r="T67">
-        <v>2.583577261821402</v>
+        <v>2.655946372796791</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.62067766308428</v>
+        <v>8.490061334855731</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7130,22 +7130,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09279639449568525</v>
+        <v>0.09274340213261209</v>
       </c>
       <c r="C68">
-        <v>143.2515262559406</v>
+        <v>140.0449423149477</v>
       </c>
       <c r="D68">
-        <v>318.3009262559406</v>
+        <v>318.6602423149477</v>
       </c>
       <c r="E68">
-        <v>233.9594</v>
+        <v>237.5253</v>
       </c>
       <c r="F68">
-        <v>235.3494</v>
+        <v>238.9153</v>
       </c>
       <c r="G68">
         <v>60.3</v>
@@ -7166,28 +7166,28 @@
         <v>106.9</v>
       </c>
       <c r="M68">
-        <v>12.5911929</v>
+        <v>12.78196855</v>
       </c>
       <c r="N68">
-        <v>94.30880710000001</v>
+        <v>94.11803145</v>
       </c>
       <c r="O68">
-        <v>11.7886008875</v>
+        <v>11.76475393125</v>
       </c>
       <c r="P68">
-        <v>82.52020621250001</v>
+        <v>82.35327751875001</v>
       </c>
       <c r="Q68">
-        <v>148.3202062125</v>
+        <v>148.15327751875</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1820592485167213</v>
+        <v>0.1859970519170064</v>
       </c>
       <c r="T68">
-        <v>2.655946372796791</v>
+        <v>2.732701490497962</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>8.490061334855731</v>
+        <v>8.363344001499676</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7212,22 +7212,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09274340213261209</v>
+        <v>0.09269040976953896</v>
       </c>
       <c r="C69">
-        <v>140.0449423149477</v>
+        <v>136.8391705232684</v>
       </c>
       <c r="D69">
-        <v>318.6602423149477</v>
+        <v>319.0203705232684</v>
       </c>
       <c r="E69">
-        <v>237.5253</v>
+        <v>241.0912</v>
       </c>
       <c r="F69">
-        <v>238.9153</v>
+        <v>242.4812</v>
       </c>
       <c r="G69">
         <v>60.3</v>
@@ -7248,28 +7248,28 @@
         <v>106.9</v>
       </c>
       <c r="M69">
-        <v>12.78196855</v>
+        <v>12.9727442</v>
       </c>
       <c r="N69">
-        <v>94.11803145</v>
+        <v>93.92725580000001</v>
       </c>
       <c r="O69">
-        <v>11.76475393125</v>
+        <v>11.740906975</v>
       </c>
       <c r="P69">
-        <v>82.35327751875001</v>
+        <v>82.18634882500001</v>
       </c>
       <c r="Q69">
-        <v>148.15327751875</v>
+        <v>147.986348825</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1859970519170064</v>
+        <v>0.1901809680298093</v>
       </c>
       <c r="T69">
-        <v>2.732701490497962</v>
+        <v>2.814253803055456</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.363344001499676</v>
+        <v>8.240353648536445</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7294,22 +7294,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09269040976953896</v>
+        <v>0.09263741740646582</v>
       </c>
       <c r="C70">
-        <v>136.8391705232684</v>
+        <v>133.6342136375264</v>
       </c>
       <c r="D70">
-        <v>319.0203705232684</v>
+        <v>319.3813136375264</v>
       </c>
       <c r="E70">
-        <v>241.0912</v>
+        <v>244.6571</v>
       </c>
       <c r="F70">
-        <v>242.4812</v>
+        <v>246.0471</v>
       </c>
       <c r="G70">
         <v>60.3</v>
@@ -7330,28 +7330,28 @@
         <v>106.9</v>
       </c>
       <c r="M70">
-        <v>12.9727442</v>
+        <v>13.16351985</v>
       </c>
       <c r="N70">
-        <v>93.92725580000001</v>
+        <v>93.73648015000001</v>
       </c>
       <c r="O70">
-        <v>11.740906975</v>
+        <v>11.71706001875</v>
       </c>
       <c r="P70">
-        <v>82.18634882500001</v>
+        <v>82.01942013125</v>
       </c>
       <c r="Q70">
-        <v>147.986348825</v>
+        <v>147.81942013125</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1901809680298093</v>
+        <v>0.1946348142144059</v>
       </c>
       <c r="T70">
-        <v>2.814253803055456</v>
+        <v>2.901067555132788</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.240353648536445</v>
+        <v>8.120928233340265</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7376,22 +7376,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09263741740646582</v>
+        <v>0.09258442504339268</v>
       </c>
       <c r="C71">
-        <v>133.6342136375264</v>
+        <v>130.4300744268353</v>
       </c>
       <c r="D71">
-        <v>319.3813136375264</v>
+        <v>319.7430744268353</v>
       </c>
       <c r="E71">
-        <v>244.6571</v>
+        <v>248.223</v>
       </c>
       <c r="F71">
-        <v>246.0471</v>
+        <v>249.613</v>
       </c>
       <c r="G71">
         <v>60.3</v>
@@ -7412,28 +7412,28 @@
         <v>106.9</v>
       </c>
       <c r="M71">
-        <v>13.16351985</v>
+        <v>13.3542955</v>
       </c>
       <c r="N71">
-        <v>93.73648015000001</v>
+        <v>93.5457045</v>
       </c>
       <c r="O71">
-        <v>11.71706001875</v>
+        <v>11.6932130625</v>
       </c>
       <c r="P71">
-        <v>82.01942013125</v>
+        <v>81.85249143749999</v>
       </c>
       <c r="Q71">
-        <v>147.81942013125</v>
+        <v>147.6524914375</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1946348142144059</v>
+        <v>0.1993855834779756</v>
       </c>
       <c r="T71">
-        <v>2.901067555132788</v>
+        <v>2.993668890681942</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.120928233340265</v>
+        <v>8.004914972863975</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7458,22 +7458,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09258442504339268</v>
+        <v>0.09253143268031955</v>
       </c>
       <c r="C72">
-        <v>130.4300744268353</v>
+        <v>127.2267556728685</v>
       </c>
       <c r="D72">
-        <v>319.7430744268353</v>
+        <v>320.1056556728685</v>
       </c>
       <c r="E72">
-        <v>248.223</v>
+        <v>251.7889</v>
       </c>
       <c r="F72">
-        <v>249.613</v>
+        <v>253.1789</v>
       </c>
       <c r="G72">
         <v>60.3</v>
@@ -7494,28 +7494,28 @@
         <v>106.9</v>
       </c>
       <c r="M72">
-        <v>13.3542955</v>
+        <v>13.54507115</v>
       </c>
       <c r="N72">
-        <v>93.5457045</v>
+        <v>93.35492885000001</v>
       </c>
       <c r="O72">
-        <v>11.6932130625</v>
+        <v>11.66936610625</v>
       </c>
       <c r="P72">
-        <v>81.85249143749999</v>
+        <v>81.68556274375001</v>
       </c>
       <c r="Q72">
-        <v>147.6524914375</v>
+        <v>147.48556274375</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1993855834779756</v>
+        <v>0.2044639920011019</v>
       </c>
       <c r="T72">
-        <v>2.993668890681942</v>
+        <v>3.092656525234486</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.004914972863975</v>
+        <v>7.892169691556032</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7540,22 +7540,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09253143268031955</v>
+        <v>0.0924784403172464</v>
       </c>
       <c r="C73">
-        <v>127.2267556728685</v>
+        <v>124.0242601699317</v>
       </c>
       <c r="D73">
-        <v>320.1056556728685</v>
+        <v>320.4690601699317</v>
       </c>
       <c r="E73">
-        <v>251.7889</v>
+        <v>255.3548</v>
       </c>
       <c r="F73">
-        <v>253.1789</v>
+        <v>256.7448</v>
       </c>
       <c r="G73">
         <v>60.3</v>
@@ -7576,28 +7576,28 @@
         <v>106.9</v>
       </c>
       <c r="M73">
-        <v>13.54507115</v>
+        <v>13.7358468</v>
       </c>
       <c r="N73">
-        <v>93.35492885000001</v>
+        <v>93.1641532</v>
       </c>
       <c r="O73">
-        <v>11.66936610625</v>
+        <v>11.64551915</v>
       </c>
       <c r="P73">
-        <v>81.68556274375001</v>
+        <v>81.51863405</v>
       </c>
       <c r="Q73">
-        <v>147.48556274375</v>
+        <v>147.31863405</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2044639920011019</v>
+        <v>0.2099051439901657</v>
       </c>
       <c r="T73">
-        <v>3.092656525234486</v>
+        <v>3.198714705112212</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.892169691556033</v>
+        <v>7.782556223617754</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7622,22 +7622,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0924784403172464</v>
+        <v>0.09242544795417326</v>
       </c>
       <c r="C74">
-        <v>124.0242601699317</v>
+        <v>120.8225907250338</v>
       </c>
       <c r="D74">
-        <v>320.4690601699317</v>
+        <v>320.8332907250338</v>
       </c>
       <c r="E74">
-        <v>255.3548</v>
+        <v>258.9207</v>
       </c>
       <c r="F74">
-        <v>256.7448</v>
+        <v>260.3107</v>
       </c>
       <c r="G74">
         <v>60.3</v>
@@ -7658,28 +7658,28 @@
         <v>106.9</v>
       </c>
       <c r="M74">
-        <v>13.7358468</v>
+        <v>13.92662245</v>
       </c>
       <c r="N74">
-        <v>93.1641532</v>
+        <v>92.97337755000001</v>
       </c>
       <c r="O74">
-        <v>11.64551915</v>
+        <v>11.62167219375</v>
       </c>
       <c r="P74">
-        <v>81.51863405</v>
+        <v>81.35170535625001</v>
       </c>
       <c r="Q74">
-        <v>147.31863405</v>
+        <v>147.15170535625</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2099051439901657</v>
+        <v>0.2157493442747158</v>
       </c>
       <c r="T74">
-        <v>3.198714705112212</v>
+        <v>3.312629046462361</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.782556223617754</v>
+        <v>7.675945864390114</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7704,22 +7704,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09242544795417326</v>
+        <v>0.09289045559110011</v>
       </c>
       <c r="C75">
-        <v>120.8225907250338</v>
+        <v>114.0885342802762</v>
       </c>
       <c r="D75">
-        <v>320.8332907250338</v>
+        <v>317.6651342802762</v>
       </c>
       <c r="E75">
-        <v>258.9207</v>
+        <v>262.4866</v>
       </c>
       <c r="F75">
-        <v>260.3107</v>
+        <v>263.8766</v>
       </c>
       <c r="G75">
         <v>60.3</v>
@@ -7740,45 +7740,45 @@
         <v>106.9</v>
       </c>
       <c r="M75">
-        <v>13.92662245</v>
+        <v>14.32849938</v>
       </c>
       <c r="N75">
-        <v>92.97337755000001</v>
+        <v>92.57150062000001</v>
       </c>
       <c r="O75">
-        <v>11.62167219375</v>
+        <v>11.5714375775</v>
       </c>
       <c r="P75">
-        <v>81.35170535625001</v>
+        <v>81.0000630425</v>
       </c>
       <c r="Q75">
-        <v>147.15170535625</v>
+        <v>146.8000630425</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2157493442747158</v>
+        <v>0.2220430984273081</v>
       </c>
       <c r="T75">
-        <v>3.312629046462361</v>
+        <v>3.43530602945483</v>
       </c>
       <c r="U75">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V75">
         <v>0.125</v>
       </c>
       <c r="W75">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y75">
-        <v>7.675945864390114</v>
+        <v>7.460655660090485</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7786,22 +7786,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09289045559110011</v>
+        <v>0.09284446322802697</v>
       </c>
       <c r="C76">
-        <v>114.0885342802762</v>
+        <v>110.8331951664889</v>
       </c>
       <c r="D76">
-        <v>317.6651342802762</v>
+        <v>317.9756951664889</v>
       </c>
       <c r="E76">
-        <v>262.4866</v>
+        <v>266.0525</v>
       </c>
       <c r="F76">
-        <v>263.8766</v>
+        <v>267.4425</v>
       </c>
       <c r="G76">
         <v>60.3</v>
@@ -7822,28 +7822,28 @@
         <v>106.9</v>
       </c>
       <c r="M76">
-        <v>14.32849938</v>
+        <v>14.52212775</v>
       </c>
       <c r="N76">
-        <v>92.57150062000001</v>
+        <v>92.37787225000001</v>
       </c>
       <c r="O76">
-        <v>11.5714375775</v>
+        <v>11.54723403125</v>
       </c>
       <c r="P76">
-        <v>81.0000630425</v>
+        <v>80.83063821875001</v>
       </c>
       <c r="Q76">
-        <v>146.8000630425</v>
+        <v>146.63063821875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2220430984273081</v>
+        <v>0.2288403529121079</v>
       </c>
       <c r="T76">
-        <v>3.43530602945483</v>
+        <v>3.567797171086698</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.460655660090485</v>
+        <v>7.361180251289279</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7868,22 +7868,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09284446322802697</v>
+        <v>0.09279847086495384</v>
       </c>
       <c r="C77">
-        <v>110.8331951664889</v>
+        <v>107.5784638779679</v>
       </c>
       <c r="D77">
-        <v>317.9756951664889</v>
+        <v>318.2868638779678</v>
       </c>
       <c r="E77">
-        <v>266.0525</v>
+        <v>269.6184</v>
       </c>
       <c r="F77">
-        <v>267.4425</v>
+        <v>271.0084</v>
       </c>
       <c r="G77">
         <v>60.3</v>
@@ -7904,28 +7904,28 @@
         <v>106.9</v>
       </c>
       <c r="M77">
-        <v>14.52212775</v>
+        <v>14.71575612</v>
       </c>
       <c r="N77">
-        <v>92.37787225000001</v>
+        <v>92.18424388000001</v>
       </c>
       <c r="O77">
-        <v>11.54723403125</v>
+        <v>11.523030485</v>
       </c>
       <c r="P77">
-        <v>80.83063821875001</v>
+        <v>80.661213395</v>
       </c>
       <c r="Q77">
-        <v>146.63063821875</v>
+        <v>146.461213395</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2288403529121079</v>
+        <v>0.236204045270641</v>
       </c>
       <c r="T77">
-        <v>3.567797171086698</v>
+        <v>3.711329241187887</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.361180251289279</v>
+        <v>7.264322616403894</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7950,22 +7950,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09279847086495384</v>
+        <v>0.0927524785018807</v>
       </c>
       <c r="C78">
-        <v>107.5784638779679</v>
+        <v>104.3243422009014</v>
       </c>
       <c r="D78">
-        <v>318.2868638779678</v>
+        <v>318.5986422009013</v>
       </c>
       <c r="E78">
-        <v>269.6184</v>
+        <v>273.1843</v>
       </c>
       <c r="F78">
-        <v>271.0084</v>
+        <v>274.5743</v>
       </c>
       <c r="G78">
         <v>60.3</v>
@@ -7986,28 +7986,28 @@
         <v>106.9</v>
       </c>
       <c r="M78">
-        <v>14.71575612</v>
+        <v>14.90938449</v>
       </c>
       <c r="N78">
-        <v>92.18424388000001</v>
+        <v>91.99061551</v>
       </c>
       <c r="O78">
-        <v>11.523030485</v>
+        <v>11.49882693875</v>
       </c>
       <c r="P78">
-        <v>80.661213395</v>
+        <v>80.49178857125</v>
       </c>
       <c r="Q78">
-        <v>146.461213395</v>
+        <v>146.29178857125</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.236204045270641</v>
+        <v>0.2442080587038291</v>
       </c>
       <c r="T78">
-        <v>3.711329241187887</v>
+        <v>3.867342360863092</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.264322616403894</v>
+        <v>7.169980764242803</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8032,22 +8032,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0927524785018807</v>
+        <v>0.09270648613880755</v>
       </c>
       <c r="C79">
-        <v>104.3243422009014</v>
+        <v>101.070831928483</v>
       </c>
       <c r="D79">
-        <v>318.5986422009013</v>
+        <v>318.911031928483</v>
       </c>
       <c r="E79">
-        <v>273.1843</v>
+        <v>276.7502</v>
       </c>
       <c r="F79">
-        <v>274.5743</v>
+        <v>278.1402</v>
       </c>
       <c r="G79">
         <v>60.3</v>
@@ -8068,28 +8068,28 @@
         <v>106.9</v>
       </c>
       <c r="M79">
-        <v>14.90938449</v>
+        <v>15.10301286</v>
       </c>
       <c r="N79">
-        <v>91.99061551</v>
+        <v>91.79698714</v>
       </c>
       <c r="O79">
-        <v>11.49882693875</v>
+        <v>11.4746233925</v>
       </c>
       <c r="P79">
-        <v>80.49178857125</v>
+        <v>80.32236374749999</v>
       </c>
       <c r="Q79">
-        <v>146.29178857125</v>
+        <v>146.1223637475</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2442080587038291</v>
+        <v>0.2529397097218525</v>
       </c>
       <c r="T79">
-        <v>3.867342360863092</v>
+        <v>4.037538491417862</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.169980764242803</v>
+        <v>7.078057933931999</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8114,22 +8114,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09270648613880755</v>
+        <v>0.09266049377573443</v>
       </c>
       <c r="C80">
-        <v>101.070831928483</v>
+        <v>97.8179348609462</v>
       </c>
       <c r="D80">
-        <v>318.911031928483</v>
+        <v>319.2240348609462</v>
       </c>
       <c r="E80">
-        <v>276.7502</v>
+        <v>280.3161</v>
       </c>
       <c r="F80">
-        <v>278.1402</v>
+        <v>281.7061</v>
       </c>
       <c r="G80">
         <v>60.3</v>
@@ -8150,28 +8150,28 @@
         <v>106.9</v>
       </c>
       <c r="M80">
-        <v>15.10301286</v>
+        <v>15.29664123</v>
       </c>
       <c r="N80">
-        <v>91.79698714</v>
+        <v>91.60335877</v>
       </c>
       <c r="O80">
-        <v>11.4746233925</v>
+        <v>11.45041984625</v>
       </c>
       <c r="P80">
-        <v>80.32236374749999</v>
+        <v>80.15293892375</v>
       </c>
       <c r="Q80">
-        <v>146.1223637475</v>
+        <v>145.95293892375</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2529397097218525</v>
+        <v>0.2625029465511163</v>
       </c>
       <c r="T80">
-        <v>4.037538491417862</v>
+        <v>4.223943777263563</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.078057933931999</v>
+        <v>6.988462263882226</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8196,22 +8196,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09266049377573443</v>
+        <v>0.09261450141266127</v>
       </c>
       <c r="C81">
-        <v>97.8179348609462</v>
+        <v>94.56565280559948</v>
       </c>
       <c r="D81">
-        <v>319.2240348609462</v>
+        <v>319.5376528055995</v>
       </c>
       <c r="E81">
-        <v>280.3161</v>
+        <v>283.882</v>
       </c>
       <c r="F81">
-        <v>281.7061</v>
+        <v>285.272</v>
       </c>
       <c r="G81">
         <v>60.3</v>
@@ -8232,28 +8232,28 @@
         <v>106.9</v>
       </c>
       <c r="M81">
-        <v>15.29664123</v>
+        <v>15.4902696</v>
       </c>
       <c r="N81">
-        <v>91.60335877</v>
+        <v>91.4097304</v>
       </c>
       <c r="O81">
-        <v>11.45041984625</v>
+        <v>11.4262163</v>
       </c>
       <c r="P81">
-        <v>80.15293892375</v>
+        <v>79.98351410000001</v>
       </c>
       <c r="Q81">
-        <v>145.95293892375</v>
+        <v>145.7835141</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2625029465511163</v>
+        <v>0.2730225070633064</v>
       </c>
       <c r="T81">
-        <v>4.223943777263563</v>
+        <v>4.428989591693832</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.988462263882226</v>
+        <v>6.901106485583698</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8278,22 +8278,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09261450141266127</v>
+        <v>0.09256850904958813</v>
       </c>
       <c r="C82">
-        <v>94.56565280559948</v>
+        <v>91.31398757685957</v>
       </c>
       <c r="D82">
-        <v>319.5376528055995</v>
+        <v>319.8518875768596</v>
       </c>
       <c r="E82">
-        <v>283.882</v>
+        <v>287.4479</v>
       </c>
       <c r="F82">
-        <v>285.272</v>
+        <v>288.8379</v>
       </c>
       <c r="G82">
         <v>60.3</v>
@@ -8314,28 +8314,28 @@
         <v>106.9</v>
       </c>
       <c r="M82">
-        <v>15.4902696</v>
+        <v>15.68389797</v>
       </c>
       <c r="N82">
-        <v>91.4097304</v>
+        <v>91.21610203</v>
       </c>
       <c r="O82">
-        <v>11.4262163</v>
+        <v>11.40201275375</v>
       </c>
       <c r="P82">
-        <v>79.98351410000001</v>
+        <v>79.81408927625</v>
       </c>
       <c r="Q82">
-        <v>145.7835141</v>
+        <v>145.61408927625</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2730225070633064</v>
+        <v>0.2846493897346744</v>
       </c>
       <c r="T82">
-        <v>4.428989591693832</v>
+        <v>4.655619176064131</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.901106485583698</v>
+        <v>6.815907640082665</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8360,22 +8360,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09256850904958813</v>
+        <v>0.09252251668651498</v>
       </c>
       <c r="C83">
-        <v>91.31398757685957</v>
+        <v>88.06294099628832</v>
       </c>
       <c r="D83">
-        <v>319.8518875768596</v>
+        <v>320.1667409962883</v>
       </c>
       <c r="E83">
-        <v>287.4479</v>
+        <v>291.0138</v>
       </c>
       <c r="F83">
-        <v>288.8379</v>
+        <v>292.4038</v>
       </c>
       <c r="G83">
         <v>60.3</v>
@@ -8396,28 +8396,28 @@
         <v>106.9</v>
       </c>
       <c r="M83">
-        <v>15.68389797</v>
+        <v>15.87752634</v>
       </c>
       <c r="N83">
-        <v>91.21610203</v>
+        <v>91.02247366</v>
       </c>
       <c r="O83">
-        <v>11.40201275375</v>
+        <v>11.3778092075</v>
       </c>
       <c r="P83">
-        <v>79.81408927625</v>
+        <v>79.6446644525</v>
       </c>
       <c r="Q83">
-        <v>145.61408927625</v>
+        <v>145.4446644525</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2846493897346744</v>
+        <v>0.2975681482584167</v>
       </c>
       <c r="T83">
-        <v>4.655619176064131</v>
+        <v>4.907429825364463</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.815907640082665</v>
+        <v>6.732786815203609</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8442,22 +8442,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09252251668651498</v>
+        <v>0.09247652432344185</v>
       </c>
       <c r="C84">
-        <v>88.06294099628832</v>
+        <v>84.81251489262667</v>
       </c>
       <c r="D84">
-        <v>320.1667409962883</v>
+        <v>320.4822148926266</v>
       </c>
       <c r="E84">
-        <v>291.0138</v>
+        <v>294.5797</v>
       </c>
       <c r="F84">
-        <v>292.4038</v>
+        <v>295.9697</v>
       </c>
       <c r="G84">
         <v>60.3</v>
@@ -8478,28 +8478,28 @@
         <v>106.9</v>
       </c>
       <c r="M84">
-        <v>15.87752634</v>
+        <v>16.07115471</v>
       </c>
       <c r="N84">
-        <v>91.02247366</v>
+        <v>90.82884529</v>
       </c>
       <c r="O84">
-        <v>11.3778092075</v>
+        <v>11.35360566125</v>
       </c>
       <c r="P84">
-        <v>79.6446644525</v>
+        <v>79.47523962875</v>
       </c>
       <c r="Q84">
-        <v>145.4446644525</v>
+        <v>145.27523962875</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2975681482584167</v>
+        <v>0.3120067607261287</v>
       </c>
       <c r="T84">
-        <v>4.907429825364463</v>
+        <v>5.188865256935422</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.732786815203609</v>
+        <v>6.651668901767421</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8524,22 +8524,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09247652432344185</v>
+        <v>0.09243053196036871</v>
       </c>
       <c r="C85">
-        <v>84.81251489262667</v>
+        <v>81.5627111018303</v>
       </c>
       <c r="D85">
-        <v>320.4822148926266</v>
+        <v>320.7983111018303</v>
       </c>
       <c r="E85">
-        <v>294.5797</v>
+        <v>298.1456</v>
       </c>
       <c r="F85">
-        <v>295.9697</v>
+        <v>299.5356</v>
       </c>
       <c r="G85">
         <v>60.3</v>
@@ -8560,28 +8560,28 @@
         <v>106.9</v>
       </c>
       <c r="M85">
-        <v>16.07115471</v>
+        <v>16.26478308</v>
       </c>
       <c r="N85">
-        <v>90.82884529</v>
+        <v>90.63521692</v>
       </c>
       <c r="O85">
-        <v>11.35360566125</v>
+        <v>11.329402115</v>
       </c>
       <c r="P85">
-        <v>79.47523962875</v>
+        <v>79.30581480500001</v>
       </c>
       <c r="Q85">
-        <v>145.27523962875</v>
+        <v>145.105814805</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3120067607261287</v>
+        <v>0.3282501997523046</v>
       </c>
       <c r="T85">
-        <v>5.188865256935422</v>
+        <v>5.505480117452753</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.651668901767421</v>
+        <v>6.57248236722257</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8606,22 +8606,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09243053196036871</v>
+        <v>0.09238453959729556</v>
       </c>
       <c r="C86">
-        <v>81.5627111018303</v>
+        <v>78.31353146710586</v>
       </c>
       <c r="D86">
-        <v>320.7983111018303</v>
+        <v>321.1150314671058</v>
       </c>
       <c r="E86">
-        <v>298.1456</v>
+        <v>301.7115</v>
       </c>
       <c r="F86">
-        <v>299.5356</v>
+        <v>303.1015</v>
       </c>
       <c r="G86">
         <v>60.3</v>
@@ -8642,28 +8642,28 @@
         <v>106.9</v>
       </c>
       <c r="M86">
-        <v>16.26478308</v>
+        <v>16.45841145</v>
       </c>
       <c r="N86">
-        <v>90.63521692</v>
+        <v>90.44158855000001</v>
       </c>
       <c r="O86">
-        <v>11.329402115</v>
+        <v>11.30519856875</v>
       </c>
       <c r="P86">
-        <v>79.30581480500001</v>
+        <v>79.13638998125001</v>
       </c>
       <c r="Q86">
-        <v>145.105814805</v>
+        <v>144.93638998125</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3282501997523044</v>
+        <v>0.3466594306486371</v>
       </c>
       <c r="T86">
-        <v>5.505480117452748</v>
+        <v>5.864310292705721</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.57248236722257</v>
+        <v>6.495159045255246</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8688,22 +8688,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09238453959729556</v>
+        <v>0.09233854723422244</v>
       </c>
       <c r="C87">
-        <v>78.31353146710586</v>
+        <v>75.06497783894554</v>
       </c>
       <c r="D87">
-        <v>321.1150314671058</v>
+        <v>321.4323778389455</v>
       </c>
       <c r="E87">
-        <v>301.7115</v>
+        <v>305.2774</v>
       </c>
       <c r="F87">
-        <v>303.1015</v>
+        <v>306.6674</v>
       </c>
       <c r="G87">
         <v>60.3</v>
@@ -8724,28 +8724,28 @@
         <v>106.9</v>
       </c>
       <c r="M87">
-        <v>16.45841145</v>
+        <v>16.65203982</v>
       </c>
       <c r="N87">
-        <v>90.44158855000001</v>
+        <v>90.24796018000001</v>
       </c>
       <c r="O87">
-        <v>11.30519856875</v>
+        <v>11.2809950225</v>
       </c>
       <c r="P87">
-        <v>79.13638998125001</v>
+        <v>78.9669651575</v>
       </c>
       <c r="Q87">
-        <v>144.93638998125</v>
+        <v>144.7669651575</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3466594306486371</v>
+        <v>0.3676985516730173</v>
       </c>
       <c r="T87">
-        <v>5.864310292705721</v>
+        <v>6.274401921566262</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.495159045255246</v>
+        <v>6.419633940077859</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8770,22 +8770,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09233854723422244</v>
+        <v>0.09229255487114929</v>
       </c>
       <c r="C88">
-        <v>75.06497783894554</v>
+        <v>71.81705207516478</v>
       </c>
       <c r="D88">
-        <v>321.4323778389455</v>
+        <v>321.7503520751648</v>
       </c>
       <c r="E88">
-        <v>305.2774</v>
+        <v>308.8433</v>
       </c>
       <c r="F88">
-        <v>306.6674</v>
+        <v>310.2333</v>
       </c>
       <c r="G88">
         <v>60.3</v>
@@ -8806,28 +8806,28 @@
         <v>106.9</v>
       </c>
       <c r="M88">
-        <v>16.65203982</v>
+        <v>16.84566819</v>
       </c>
       <c r="N88">
-        <v>90.24796018000001</v>
+        <v>90.05433181000001</v>
       </c>
       <c r="O88">
-        <v>11.2809950225</v>
+        <v>11.25679147625</v>
       </c>
       <c r="P88">
-        <v>78.9669651575</v>
+        <v>78.79754033375001</v>
       </c>
       <c r="Q88">
-        <v>144.7669651575</v>
+        <v>144.59754033375</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3676985516730173</v>
+        <v>0.3919744605473022</v>
       </c>
       <c r="T88">
-        <v>6.274401921566262</v>
+        <v>6.747584570251499</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.419633940077859</v>
+        <v>6.345845044214896</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8852,22 +8852,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09229255487114929</v>
+        <v>0.09224656250807615</v>
       </c>
       <c r="C89">
-        <v>71.81705207516478</v>
+        <v>68.5697560409368</v>
       </c>
       <c r="D89">
-        <v>321.7503520751648</v>
+        <v>322.0689560409368</v>
       </c>
       <c r="E89">
-        <v>308.8433</v>
+        <v>312.4092</v>
       </c>
       <c r="F89">
-        <v>310.2333</v>
+        <v>313.7992</v>
       </c>
       <c r="G89">
         <v>60.3</v>
@@ -8888,28 +8888,28 @@
         <v>106.9</v>
       </c>
       <c r="M89">
-        <v>16.84566819</v>
+        <v>17.03929656</v>
       </c>
       <c r="N89">
-        <v>90.05433181000001</v>
+        <v>89.86070344000001</v>
       </c>
       <c r="O89">
-        <v>11.25679147625</v>
+        <v>11.23258793</v>
       </c>
       <c r="P89">
-        <v>78.79754033375001</v>
+        <v>78.62811551000001</v>
       </c>
       <c r="Q89">
-        <v>144.59754033375</v>
+        <v>144.42811551</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3919744605473022</v>
+        <v>0.4202963542339679</v>
       </c>
       <c r="T89">
-        <v>6.747584570251499</v>
+        <v>7.299630993717612</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.345845044214896</v>
+        <v>6.273733168712454</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8934,22 +8934,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09224656250807615</v>
+        <v>0.09220057014500301</v>
       </c>
       <c r="C90">
-        <v>68.5697560409368</v>
+        <v>65.3230916088304</v>
       </c>
       <c r="D90">
-        <v>322.0689560409368</v>
+        <v>322.3881916088304</v>
       </c>
       <c r="E90">
-        <v>312.4092</v>
+        <v>315.9751</v>
       </c>
       <c r="F90">
-        <v>313.7992</v>
+        <v>317.3651</v>
       </c>
       <c r="G90">
         <v>60.3</v>
@@ -8970,28 +8970,28 @@
         <v>106.9</v>
       </c>
       <c r="M90">
-        <v>17.03929656</v>
+        <v>17.23292493</v>
       </c>
       <c r="N90">
-        <v>89.86070344000001</v>
+        <v>89.66707507000001</v>
       </c>
       <c r="O90">
-        <v>11.23258793</v>
+        <v>11.20838438375</v>
       </c>
       <c r="P90">
-        <v>78.62811551000001</v>
+        <v>78.45869068625001</v>
       </c>
       <c r="Q90">
-        <v>144.42811551</v>
+        <v>144.25869068625</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4202963542339679</v>
+        <v>0.453767683136391</v>
       </c>
       <c r="T90">
-        <v>7.299630993717612</v>
+        <v>7.952049494177562</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.273733168712454</v>
+        <v>6.203241784794336</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9016,22 +9016,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09220057014500301</v>
+        <v>0.09215457778192987</v>
       </c>
       <c r="C91">
-        <v>65.3230916088304</v>
+        <v>62.07706065884565</v>
       </c>
       <c r="D91">
-        <v>322.3881916088304</v>
+        <v>322.7080606588456</v>
       </c>
       <c r="E91">
-        <v>315.9751</v>
+        <v>319.541</v>
       </c>
       <c r="F91">
-        <v>317.3651</v>
+        <v>320.931</v>
       </c>
       <c r="G91">
         <v>60.3</v>
@@ -9052,28 +9052,28 @@
         <v>106.9</v>
       </c>
       <c r="M91">
-        <v>17.23292493</v>
+        <v>17.4265533</v>
       </c>
       <c r="N91">
-        <v>89.66707507000001</v>
+        <v>89.47344670000001</v>
       </c>
       <c r="O91">
-        <v>11.20838438375</v>
+        <v>11.1841808375</v>
       </c>
       <c r="P91">
-        <v>78.45869068625001</v>
+        <v>78.2892658625</v>
       </c>
       <c r="Q91">
-        <v>144.25869068625</v>
+        <v>144.0892658625</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.453767683136391</v>
+        <v>0.4939332778192987</v>
       </c>
       <c r="T91">
-        <v>7.952049494177562</v>
+        <v>8.734951694729503</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.203241784794336</v>
+        <v>6.1343168760744</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9098,22 +9098,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09215457778192987</v>
+        <v>0.09290483541885672</v>
       </c>
       <c r="C92">
-        <v>62.07706065884565</v>
+        <v>53.37125973669464</v>
       </c>
       <c r="D92">
-        <v>322.7080606588456</v>
+        <v>317.5681597366946</v>
       </c>
       <c r="E92">
-        <v>319.541</v>
+        <v>323.1069</v>
       </c>
       <c r="F92">
-        <v>320.931</v>
+        <v>324.4969</v>
       </c>
       <c r="G92">
         <v>60.3</v>
@@ -9134,45 +9134,45 @@
         <v>106.9</v>
       </c>
       <c r="M92">
-        <v>17.4265533</v>
+        <v>17.94467857</v>
       </c>
       <c r="N92">
-        <v>89.47344670000001</v>
+        <v>88.95532143</v>
       </c>
       <c r="O92">
-        <v>11.1841808375</v>
+        <v>11.11941517875</v>
       </c>
       <c r="P92">
-        <v>78.2892658625</v>
+        <v>77.83590625124999</v>
       </c>
       <c r="Q92">
-        <v>144.0892658625</v>
+        <v>143.63590625125</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4939332778192987</v>
+        <v>0.5430245602095193</v>
       </c>
       <c r="T92">
-        <v>8.734951694729503</v>
+        <v>9.691832162070764</v>
       </c>
       <c r="U92">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V92">
         <v>0.125</v>
       </c>
       <c r="W92">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>6.1343168760744</v>
+        <v>5.957197816778726</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9180,22 +9180,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09290483541885672</v>
+        <v>0.09286759305578358</v>
       </c>
       <c r="C93">
-        <v>53.37125973669464</v>
+        <v>50.05663642066202</v>
       </c>
       <c r="D93">
-        <v>317.5681597366946</v>
+        <v>317.819436420662</v>
       </c>
       <c r="E93">
-        <v>323.1069</v>
+        <v>326.6728</v>
       </c>
       <c r="F93">
-        <v>324.4969</v>
+        <v>328.0628</v>
       </c>
       <c r="G93">
         <v>60.3</v>
@@ -9216,28 +9216,28 @@
         <v>106.9</v>
       </c>
       <c r="M93">
-        <v>17.94467857</v>
+        <v>18.14187284</v>
       </c>
       <c r="N93">
-        <v>88.95532143</v>
+        <v>88.75812716</v>
       </c>
       <c r="O93">
-        <v>11.11941517875</v>
+        <v>11.094765895</v>
       </c>
       <c r="P93">
-        <v>77.83590625124999</v>
+        <v>77.66336126500001</v>
       </c>
       <c r="Q93">
-        <v>143.63590625125</v>
+        <v>143.463361265</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5430245602095193</v>
+        <v>0.6043886631972951</v>
       </c>
       <c r="T93">
-        <v>9.691832162070764</v>
+        <v>10.88793274624734</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.957197816778726</v>
+        <v>5.892445666596349</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9262,22 +9262,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09286759305578358</v>
+        <v>0.09283035069271044</v>
       </c>
       <c r="C94">
-        <v>50.05663642066202</v>
+        <v>46.7424110662588</v>
       </c>
       <c r="D94">
-        <v>317.819436420662</v>
+        <v>318.0711110662588</v>
       </c>
       <c r="E94">
-        <v>326.6728</v>
+        <v>330.2387</v>
       </c>
       <c r="F94">
-        <v>328.0628</v>
+        <v>331.6287</v>
       </c>
       <c r="G94">
         <v>60.3</v>
@@ -9298,28 +9298,28 @@
         <v>106.9</v>
       </c>
       <c r="M94">
-        <v>18.14187284</v>
+        <v>18.33906711</v>
       </c>
       <c r="N94">
-        <v>88.75812716</v>
+        <v>88.56093289</v>
       </c>
       <c r="O94">
-        <v>11.094765895</v>
+        <v>11.07011661125</v>
       </c>
       <c r="P94">
-        <v>77.66336126500001</v>
+        <v>77.49081627875</v>
       </c>
       <c r="Q94">
-        <v>143.463361265</v>
+        <v>143.29081627875</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6043886631972951</v>
+        <v>0.683285367038721</v>
       </c>
       <c r="T94">
-        <v>10.88793274624734</v>
+        <v>12.42577635447437</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.892445666596349</v>
+        <v>5.829086035772733</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9344,22 +9344,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09283035069271044</v>
+        <v>0.0927931083296373</v>
       </c>
       <c r="C95">
-        <v>46.7424110662588</v>
+        <v>43.42858461964698</v>
       </c>
       <c r="D95">
-        <v>318.0711110662588</v>
+        <v>318.323184619647</v>
       </c>
       <c r="E95">
-        <v>330.2387</v>
+        <v>333.8046</v>
       </c>
       <c r="F95">
-        <v>331.6287</v>
+        <v>335.1946</v>
       </c>
       <c r="G95">
         <v>60.3</v>
@@ -9380,28 +9380,28 @@
         <v>106.9</v>
       </c>
       <c r="M95">
-        <v>18.33906711</v>
+        <v>18.53626138</v>
       </c>
       <c r="N95">
-        <v>88.56093289</v>
+        <v>88.36373862000001</v>
       </c>
       <c r="O95">
-        <v>11.07011661125</v>
+        <v>11.0454673275</v>
       </c>
       <c r="P95">
-        <v>77.49081627875</v>
+        <v>77.3182712925</v>
       </c>
       <c r="Q95">
-        <v>143.29081627875</v>
+        <v>143.1182712925</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.683285367038721</v>
+        <v>0.7884809721606223</v>
       </c>
       <c r="T95">
-        <v>12.42577635447437</v>
+        <v>14.47623449877707</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.829086035772733</v>
+        <v>5.767074482200683</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9426,22 +9426,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0927931083296373</v>
+        <v>0.09275586596656417</v>
       </c>
       <c r="C96">
-        <v>43.42858461964698</v>
+        <v>40.1151580299902</v>
       </c>
       <c r="D96">
-        <v>318.323184619647</v>
+        <v>318.5756580299902</v>
       </c>
       <c r="E96">
-        <v>333.8046</v>
+        <v>337.3705</v>
       </c>
       <c r="F96">
-        <v>335.1946</v>
+        <v>338.7605</v>
       </c>
       <c r="G96">
         <v>60.3</v>
@@ -9462,28 +9462,28 @@
         <v>106.9</v>
       </c>
       <c r="M96">
-        <v>18.53626138</v>
+        <v>18.73345565</v>
       </c>
       <c r="N96">
-        <v>88.36373862000001</v>
+        <v>88.16654435000001</v>
       </c>
       <c r="O96">
-        <v>11.0454673275</v>
+        <v>11.02081804375</v>
       </c>
       <c r="P96">
-        <v>77.3182712925</v>
+        <v>77.14572630625001</v>
       </c>
       <c r="Q96">
-        <v>143.1182712925</v>
+        <v>142.94572630625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7884809721606223</v>
+        <v>0.9357548193312845</v>
       </c>
       <c r="T96">
-        <v>14.47623449877707</v>
+        <v>17.34687590080086</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.767074482200683</v>
+        <v>5.706368435019622</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9508,22 +9508,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09275586596656417</v>
+        <v>0.09271862360349102</v>
       </c>
       <c r="C97">
-        <v>40.1151580299902</v>
+        <v>36.80213224946624</v>
       </c>
       <c r="D97">
-        <v>318.5756580299902</v>
+        <v>318.8285322494662</v>
       </c>
       <c r="E97">
-        <v>337.3705</v>
+        <v>340.9364</v>
       </c>
       <c r="F97">
-        <v>338.7605</v>
+        <v>342.3264</v>
       </c>
       <c r="G97">
         <v>60.3</v>
@@ -9544,28 +9544,28 @@
         <v>106.9</v>
       </c>
       <c r="M97">
-        <v>18.73345565</v>
+        <v>18.93064992</v>
       </c>
       <c r="N97">
-        <v>88.16654435000001</v>
+        <v>87.96935008</v>
       </c>
       <c r="O97">
-        <v>11.02081804375</v>
+        <v>10.99616876</v>
       </c>
       <c r="P97">
-        <v>77.14572630625001</v>
+        <v>76.97318131999999</v>
       </c>
       <c r="Q97">
-        <v>142.94572630625</v>
+        <v>142.77318132</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9357548193312845</v>
+        <v>1.156665590087278</v>
       </c>
       <c r="T97">
-        <v>17.34687590080086</v>
+        <v>21.65283800383655</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.706368435019622</v>
+        <v>5.646927097154834</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9590,22 +9590,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09271862360349103</v>
+        <v>0.09268138124041789</v>
       </c>
       <c r="C98">
-        <v>36.80213224946613</v>
+        <v>33.48950823327772</v>
       </c>
       <c r="D98">
-        <v>318.8285322494661</v>
+        <v>319.0818082332777</v>
       </c>
       <c r="E98">
-        <v>340.9364</v>
+        <v>344.5023</v>
       </c>
       <c r="F98">
-        <v>342.3264</v>
+        <v>345.8923</v>
       </c>
       <c r="G98">
         <v>60.3</v>
@@ -9626,28 +9626,28 @@
         <v>106.9</v>
       </c>
       <c r="M98">
-        <v>18.93064992</v>
+        <v>19.12784419</v>
       </c>
       <c r="N98">
-        <v>87.96935008</v>
+        <v>87.77215581</v>
       </c>
       <c r="O98">
-        <v>10.99616876</v>
+        <v>10.97151947625</v>
       </c>
       <c r="P98">
-        <v>76.97318131999999</v>
+        <v>76.80063633375001</v>
       </c>
       <c r="Q98">
-        <v>142.77318132</v>
+        <v>142.60063633375</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.156665590087275</v>
+        <v>1.524850208013928</v>
       </c>
       <c r="T98">
-        <v>21.65283800383649</v>
+        <v>28.82944150889594</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.646927097154834</v>
+        <v>5.588711353885197</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9672,22 +9672,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09268138124041789</v>
+        <v>0.09264413887734474</v>
       </c>
       <c r="C99">
-        <v>33.48950823327772</v>
+        <v>30.17728693966563</v>
       </c>
       <c r="D99">
-        <v>319.0818082332777</v>
+        <v>319.3354869396656</v>
       </c>
       <c r="E99">
-        <v>344.5023</v>
+        <v>348.0682</v>
       </c>
       <c r="F99">
-        <v>345.8923</v>
+        <v>349.4582</v>
       </c>
       <c r="G99">
         <v>60.3</v>
@@ -9708,28 +9708,28 @@
         <v>106.9</v>
       </c>
       <c r="M99">
-        <v>19.12784419</v>
+        <v>19.32503846</v>
       </c>
       <c r="N99">
-        <v>87.77215581</v>
+        <v>87.57496154</v>
       </c>
       <c r="O99">
-        <v>10.97151947625</v>
+        <v>10.9468701925</v>
       </c>
       <c r="P99">
-        <v>76.80063633375001</v>
+        <v>76.6280913475</v>
       </c>
       <c r="Q99">
-        <v>142.60063633375</v>
+        <v>142.4280913475</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.524850208013928</v>
+        <v>2.261219443867235</v>
       </c>
       <c r="T99">
-        <v>28.82944150889594</v>
+        <v>43.18264851901483</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9746,7 +9746,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.588711353885197</v>
+        <v>5.531683687008818</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9754,22 +9754,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09264413887734474</v>
+        <v>0.09260689651427159</v>
       </c>
       <c r="C100">
-        <v>30.17728693966563</v>
+        <v>26.86546932992024</v>
       </c>
       <c r="D100">
-        <v>319.3354869396656</v>
+        <v>319.5895693299202</v>
       </c>
       <c r="E100">
-        <v>348.0682</v>
+        <v>351.6341</v>
       </c>
       <c r="F100">
-        <v>349.4582</v>
+        <v>353.0241</v>
       </c>
       <c r="G100">
         <v>60.3</v>
@@ -9790,28 +9790,28 @@
         <v>106.9</v>
       </c>
       <c r="M100">
-        <v>19.32503846</v>
+        <v>19.52223273</v>
       </c>
       <c r="N100">
-        <v>87.57496154</v>
+        <v>87.37776727000001</v>
       </c>
       <c r="O100">
-        <v>10.9468701925</v>
+        <v>10.92222090875</v>
       </c>
       <c r="P100">
-        <v>76.6280913475</v>
+        <v>76.45554636125</v>
       </c>
       <c r="Q100">
-        <v>142.4280913475</v>
+        <v>142.25554636125</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.261219443867235</v>
+        <v>4.470327151427156</v>
       </c>
       <c r="T100">
-        <v>43.18264851901483</v>
+        <v>86.24226954937149</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9828,91 +9828,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.531683687008818</v>
+        <v>5.475808094210749</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09260689651427159</v>
-      </c>
-      <c r="C101">
-        <v>26.86546932992024</v>
-      </c>
-      <c r="D101">
-        <v>319.5895693299202</v>
-      </c>
-      <c r="E101">
-        <v>351.6341</v>
-      </c>
-      <c r="F101">
-        <v>353.0241</v>
-      </c>
-      <c r="G101">
-        <v>60.3</v>
-      </c>
-      <c r="H101">
-        <v>355.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>172.7</v>
-      </c>
-      <c r="K101">
-        <v>65.79999999999998</v>
-      </c>
-      <c r="L101">
-        <v>106.9</v>
-      </c>
-      <c r="M101">
-        <v>19.52223273</v>
-      </c>
-      <c r="N101">
-        <v>87.37776727000001</v>
-      </c>
-      <c r="O101">
-        <v>10.92222090875</v>
-      </c>
-      <c r="P101">
-        <v>76.45554636125</v>
-      </c>
-      <c r="Q101">
-        <v>142.25554636125</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.470327151427156</v>
-      </c>
-      <c r="T101">
-        <v>86.24226954937149</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.125</v>
-      </c>
-      <c r="W101">
-        <v>0.0483875</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.475808094210749</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
